--- a/data/crops/rothc_support/permcrops_baseline_rothc_scenarios_FAOGAEZ.xlsx
+++ b/data/crops/rothc_support/permcrops_baseline_rothc_scenarios_FAOGAEZ.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://worldwildlifefund-my.sharepoint.com/personal/cristobal_loyola_wwfus_org/Documents/Documents/203. Python projects/SBTN_Test/data/crops/rothc_support/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="208" documentId="11_9BC43EBF71FB3192BEA8278AF65FF74D9D56121C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{70E7F683-0C5A-4707-8A66-F1D3EF33C15B}"/>
+  <xr:revisionPtr revIDLastSave="212" documentId="11_9BC43EBF71FB3192BEA8278AF65FF74D9D56121C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D9D8AAEC-AC02-48AF-987B-D4B903BAF0AE}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -52,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1551" uniqueCount="551">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1543" uniqueCount="551">
   <si>
     <t>lu_fp</t>
   </si>
@@ -2427,7 +2427,7 @@
         <v>445</v>
       </c>
       <c r="T2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U2" s="11" t="s">
         <v>548</v>
@@ -2494,7 +2494,7 @@
         <v>414</v>
       </c>
       <c r="T3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U3" s="11" t="s">
         <v>548</v>
@@ -2561,7 +2561,7 @@
         <v>424</v>
       </c>
       <c r="T4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U4" s="11" t="s">
         <v>548</v>
@@ -2628,7 +2628,7 @@
         <v>430</v>
       </c>
       <c r="T5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U5" s="11" t="s">
         <v>548</v>
@@ -2695,7 +2695,7 @@
         <v>427</v>
       </c>
       <c r="T6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U6" s="11" t="s">
         <v>548</v>
@@ -2762,7 +2762,7 @@
         <v>445</v>
       </c>
       <c r="T7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U7" s="11" t="s">
         <v>548</v>
@@ -2829,7 +2829,7 @@
         <v>475</v>
       </c>
       <c r="T8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U8" s="11" t="s">
         <v>548</v>
@@ -2896,7 +2896,7 @@
         <v>479</v>
       </c>
       <c r="T9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U9" s="11" t="s">
         <v>548</v>
@@ -2963,7 +2963,7 @@
         <v>445</v>
       </c>
       <c r="T10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U10" s="11" t="s">
         <v>548</v>
@@ -3027,7 +3027,7 @@
         <v>445</v>
       </c>
       <c r="T11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U11" s="11" t="s">
         <v>548</v>
@@ -3068,9 +3068,7 @@
       <c r="I12" s="7" t="s">
         <v>381</v>
       </c>
-      <c r="J12" s="8" t="s">
-        <v>380</v>
-      </c>
+      <c r="J12" s="8"/>
       <c r="M12" t="b">
         <v>0</v>
       </c>
@@ -3135,9 +3133,7 @@
       <c r="I13" s="5" t="s">
         <v>384</v>
       </c>
-      <c r="J13" s="6" t="s">
-        <v>380</v>
-      </c>
+      <c r="J13" s="6"/>
       <c r="M13" t="b">
         <v>0</v>
       </c>
@@ -3202,9 +3198,7 @@
       <c r="I14" s="7" t="s">
         <v>387</v>
       </c>
-      <c r="J14" s="8" t="s">
-        <v>380</v>
-      </c>
+      <c r="J14" s="8"/>
       <c r="M14" t="b">
         <v>0</v>
       </c>
@@ -3269,9 +3263,7 @@
       <c r="I15" s="5" t="s">
         <v>390</v>
       </c>
-      <c r="J15" s="6" t="s">
-        <v>380</v>
-      </c>
+      <c r="J15" s="6"/>
       <c r="M15" t="b">
         <v>0</v>
       </c>
@@ -3400,9 +3392,7 @@
       <c r="I17" s="7" t="s">
         <v>393</v>
       </c>
-      <c r="J17" s="8" t="s">
-        <v>380</v>
-      </c>
+      <c r="J17" s="8"/>
       <c r="M17" t="b">
         <v>0</v>
       </c>
@@ -3467,9 +3457,7 @@
       <c r="I18" s="5" t="s">
         <v>396</v>
       </c>
-      <c r="J18" s="6" t="s">
-        <v>380</v>
-      </c>
+      <c r="J18" s="6"/>
       <c r="M18" t="b">
         <v>0</v>
       </c>
@@ -3534,9 +3522,7 @@
       <c r="I19" s="7" t="s">
         <v>399</v>
       </c>
-      <c r="J19" s="8" t="s">
-        <v>380</v>
-      </c>
+      <c r="J19" s="8"/>
       <c r="M19" t="b">
         <v>0</v>
       </c>
@@ -3668,9 +3654,7 @@
       <c r="I21" s="7" t="s">
         <v>406</v>
       </c>
-      <c r="J21" s="8" t="s">
-        <v>380</v>
-      </c>
+      <c r="J21" s="8"/>
       <c r="M21" t="b">
         <v>0</v>
       </c>

--- a/data/crops/rothc_support/permcrops_baseline_rothc_scenarios_FAOGAEZ.xlsx
+++ b/data/crops/rothc_support/permcrops_baseline_rothc_scenarios_FAOGAEZ.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://worldwildlifefund-my.sharepoint.com/personal/cristobal_loyola_wwfus_org/Documents/Documents/203. Python projects/SBTN_Test/data/crops/rothc_support/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="212" documentId="11_9BC43EBF71FB3192BEA8278AF65FF74D9D56121C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D9D8AAEC-AC02-48AF-987B-D4B903BAF0AE}"/>
+  <xr:revisionPtr revIDLastSave="217" documentId="11_9BC43EBF71FB3192BEA8278AF65FF74D9D56121C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C1DE1AF6-9046-43DE-B133-91DE2DFDBE38}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -52,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1543" uniqueCount="551">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1549" uniqueCount="557">
   <si>
     <t>lu_fp</t>
   </si>
@@ -70,9 +70,6 @@
   </si>
   <si>
     <t>residue_runs</t>
-  </si>
-  <si>
-    <t>../LEAFs/SOC/rasters</t>
   </si>
   <si>
     <t>crop_name</t>
@@ -1753,12 +1750,33 @@
       <t>)</t>
     </r>
   </si>
+  <si>
+    <t>../LEAFs/SOC/rasters_clipped</t>
+  </si>
+  <si>
+    <t>apply_local_zscore</t>
+  </si>
+  <si>
+    <t>apply_soc_clip</t>
+  </si>
+  <si>
+    <t>soc_global_percentile_cap</t>
+  </si>
+  <si>
+    <t>max_annual_soc_gain</t>
+  </si>
+  <si>
+    <t>max_soc_tc_ha</t>
+  </si>
+  <si>
+    <t>yield_global_percentile_cap</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1801,6 +1819,13 @@
     <font>
       <sz val="7"/>
       <color rgb="FF89DDFF"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="7"/>
+      <color rgb="FFFF7EDB"/>
       <name val="Consolas"/>
       <family val="3"/>
     </font>
@@ -1871,7 +1896,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -1888,6 +1913,9 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2285,7 +2313,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:W21"/>
+  <dimension ref="A1:AC21"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="2" width="13.54296875" bestFit="1" customWidth="1"/>
@@ -2301,15 +2329,15 @@
     <col min="19" max="19" width="10.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:29" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" t="s">
         <v>7</v>
       </c>
-      <c r="B1" t="s">
-        <v>8</v>
-      </c>
       <c r="C1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D1" t="s">
         <v>1</v>
@@ -2327,82 +2355,100 @@
         <v>2</v>
       </c>
       <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
         <v>9</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>10</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>11</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>12</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>13</v>
-      </c>
-      <c r="N1" t="s">
-        <v>14</v>
       </c>
       <c r="O1" t="s">
         <v>5</v>
       </c>
       <c r="P1" s="3" t="s">
+        <v>406</v>
+      </c>
+      <c r="Q1" s="3" t="s">
         <v>407</v>
       </c>
-      <c r="Q1" s="3" t="s">
+      <c r="R1" s="3" t="s">
         <v>408</v>
       </c>
-      <c r="R1" s="3" t="s">
+      <c r="S1" s="3" t="s">
         <v>409</v>
       </c>
-      <c r="S1" s="3" t="s">
-        <v>410</v>
-      </c>
       <c r="T1" s="9" t="s">
+        <v>543</v>
+      </c>
+      <c r="U1" s="9" t="s">
         <v>544</v>
       </c>
-      <c r="U1" s="9" t="s">
+      <c r="V1" s="9" t="s">
         <v>545</v>
       </c>
-      <c r="V1" s="9" t="s">
+      <c r="W1" s="10" t="s">
         <v>546</v>
       </c>
-      <c r="W1" s="10" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="2" spans="1:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="X1" s="9" t="s">
+        <v>551</v>
+      </c>
+      <c r="Y1" s="12" t="s">
+        <v>552</v>
+      </c>
+      <c r="Z1" s="12" t="s">
+        <v>553</v>
+      </c>
+      <c r="AA1" s="12" t="s">
+        <v>554</v>
+      </c>
+      <c r="AB1" s="12" t="s">
+        <v>555</v>
+      </c>
+      <c r="AC1" s="12" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="2" spans="1:29" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D2" s="2">
         <v>14</v>
       </c>
       <c r="E2" t="s">
-        <v>6</v>
+        <v>550</v>
       </c>
       <c r="F2" t="str">
         <f>"RothC model results for year 2030 for "&amp;A2&amp;", "&amp;IF(C2="irr","irrigated","rainfed")</f>
         <v>RothC model results for year 2030 for Apple, irrigated</v>
       </c>
       <c r="G2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H2" t="s">
+        <v>332</v>
+      </c>
+      <c r="I2" t="s">
         <v>333</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
         <v>334</v>
-      </c>
-      <c r="J2" t="s">
-        <v>335</v>
       </c>
       <c r="M2" t="b">
         <v>0</v>
@@ -2418,58 +2464,70 @@
         <v>C:\Users\loyola\OneDrive - World Wildlife Fund, Inc\Documents\203. Python projects\SBTN_Test\data\crops\FAO_GAEZ\YIELDS\GAEZ-V5.RES06-YLD.FRT.WSI.tif</v>
       </c>
       <c r="Q2" s="7" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="R2" s="7" t="s">
+        <v>443</v>
+      </c>
+      <c r="S2" s="8" t="s">
         <v>444</v>
-      </c>
-      <c r="S2" s="8" t="s">
-        <v>445</v>
       </c>
       <c r="T2" t="b">
         <v>0</v>
       </c>
       <c r="U2" s="11" t="s">
+        <v>547</v>
+      </c>
+      <c r="V2" t="s">
         <v>548</v>
       </c>
-      <c r="V2" t="s">
+      <c r="W2" t="s">
         <v>549</v>
       </c>
-      <c r="W2" t="s">
-        <v>550</v>
-      </c>
-    </row>
-    <row r="3" spans="1:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="X2" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y2" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z2">
+        <v>99.5</v>
+      </c>
+      <c r="AC2">
+        <v>99.5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:29" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B3" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D3" s="2">
         <v>14</v>
       </c>
       <c r="E3" t="s">
-        <v>6</v>
+        <v>550</v>
       </c>
       <c r="F3" t="str">
         <f t="shared" ref="F3:F21" si="0">"RothC model results for year 2030 for "&amp;A3&amp;", "&amp;IF(C3="irr","irrigated","rainfed")</f>
         <v>RothC model results for year 2030 for Banana, irrigated</v>
       </c>
       <c r="G3" s="5" t="s">
+        <v>349</v>
+      </c>
+      <c r="H3" s="5" t="s">
         <v>350</v>
       </c>
-      <c r="H3" s="5" t="s">
+      <c r="I3" s="5" t="s">
+        <v>352</v>
+      </c>
+      <c r="J3" s="6" t="s">
         <v>351</v>
-      </c>
-      <c r="I3" s="5" t="s">
-        <v>353</v>
-      </c>
-      <c r="J3" s="6" t="s">
-        <v>352</v>
       </c>
       <c r="M3" t="b">
         <v>0</v>
@@ -2485,58 +2543,70 @@
         <v>C:\Users\loyola\OneDrive - World Wildlife Fund, Inc\Documents\203. Python projects\SBTN_Test\data\crops\FAO_GAEZ\YIELDS\GAEZ-V5.RES06-YLD.BAN.WSI.tif</v>
       </c>
       <c r="Q3" s="5" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="R3" s="5" t="s">
+        <v>412</v>
+      </c>
+      <c r="S3" s="6" t="s">
         <v>413</v>
-      </c>
-      <c r="S3" s="6" t="s">
-        <v>414</v>
       </c>
       <c r="T3" t="b">
         <v>0</v>
       </c>
       <c r="U3" s="11" t="s">
+        <v>547</v>
+      </c>
+      <c r="V3" t="s">
         <v>548</v>
       </c>
-      <c r="V3" t="s">
+      <c r="W3" t="s">
         <v>549</v>
       </c>
-      <c r="W3" t="s">
-        <v>550</v>
-      </c>
-    </row>
-    <row r="4" spans="1:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="X3" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y3" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z3">
+        <v>99.5</v>
+      </c>
+      <c r="AC3">
+        <v>99.5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:29" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B4" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D4" s="2">
         <v>14</v>
       </c>
       <c r="E4" t="s">
-        <v>6</v>
+        <v>550</v>
       </c>
       <c r="F4" t="str">
         <f t="shared" si="0"/>
         <v>RothC model results for year 2030 for Cocoa, irrigated</v>
       </c>
       <c r="G4" s="7" t="s">
+        <v>353</v>
+      </c>
+      <c r="H4" s="7" t="s">
         <v>354</v>
       </c>
-      <c r="H4" s="7" t="s">
+      <c r="I4" s="7" t="s">
+        <v>356</v>
+      </c>
+      <c r="J4" s="8" t="s">
         <v>355</v>
-      </c>
-      <c r="I4" s="7" t="s">
-        <v>357</v>
-      </c>
-      <c r="J4" s="8" t="s">
-        <v>356</v>
       </c>
       <c r="M4" t="b">
         <v>0</v>
@@ -2552,58 +2622,70 @@
         <v>C:\Users\loyola\OneDrive - World Wildlife Fund, Inc\Documents\203. Python projects\SBTN_Test\data\crops\FAO_GAEZ\YIELDS\GAEZ-V5.RES06-YLD.COC.WSI.tif</v>
       </c>
       <c r="Q4" s="7" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="R4" s="7" t="s">
+        <v>422</v>
+      </c>
+      <c r="S4" s="8" t="s">
         <v>423</v>
-      </c>
-      <c r="S4" s="8" t="s">
-        <v>424</v>
       </c>
       <c r="T4" t="b">
         <v>0</v>
       </c>
       <c r="U4" s="11" t="s">
+        <v>547</v>
+      </c>
+      <c r="V4" t="s">
         <v>548</v>
       </c>
-      <c r="V4" t="s">
+      <c r="W4" t="s">
         <v>549</v>
       </c>
-      <c r="W4" t="s">
-        <v>550</v>
-      </c>
-    </row>
-    <row r="5" spans="1:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="X4" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y4" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z4">
+        <v>99.5</v>
+      </c>
+      <c r="AC4">
+        <v>99.5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:29" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B5" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D5" s="2">
         <v>14</v>
       </c>
       <c r="E5" t="s">
-        <v>6</v>
+        <v>550</v>
       </c>
       <c r="F5" t="str">
         <f t="shared" si="0"/>
         <v>RothC model results for year 2030 for Coconut, irrigated</v>
       </c>
       <c r="G5" s="5" t="s">
+        <v>357</v>
+      </c>
+      <c r="H5" s="5" t="s">
         <v>358</v>
       </c>
-      <c r="H5" s="5" t="s">
+      <c r="I5" s="5" t="s">
+        <v>360</v>
+      </c>
+      <c r="J5" s="6" t="s">
         <v>359</v>
-      </c>
-      <c r="I5" s="5" t="s">
-        <v>361</v>
-      </c>
-      <c r="J5" s="6" t="s">
-        <v>360</v>
       </c>
       <c r="M5" t="b">
         <v>0</v>
@@ -2619,58 +2701,70 @@
         <v>C:\Users\loyola\OneDrive - World Wildlife Fund, Inc\Documents\203. Python projects\SBTN_Test\data\crops\FAO_GAEZ\YIELDS\GAEZ-V5.RES06-YLD.CON.WSI.tif</v>
       </c>
       <c r="Q5" s="7" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="R5" s="7" t="s">
+        <v>428</v>
+      </c>
+      <c r="S5" s="8" t="s">
         <v>429</v>
-      </c>
-      <c r="S5" s="8" t="s">
-        <v>430</v>
       </c>
       <c r="T5" t="b">
         <v>0</v>
       </c>
       <c r="U5" s="11" t="s">
+        <v>547</v>
+      </c>
+      <c r="V5" t="s">
         <v>548</v>
       </c>
-      <c r="V5" t="s">
+      <c r="W5" t="s">
         <v>549</v>
       </c>
-      <c r="W5" t="s">
-        <v>550</v>
-      </c>
-    </row>
-    <row r="6" spans="1:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="X5" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y5" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z5">
+        <v>99.5</v>
+      </c>
+      <c r="AC5">
+        <v>99.5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:29" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B6" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D6" s="2">
         <v>14</v>
       </c>
       <c r="E6" t="s">
-        <v>6</v>
+        <v>550</v>
       </c>
       <c r="F6" t="str">
         <f t="shared" si="0"/>
         <v>RothC model results for year 2030 for Coffee, irrigated</v>
       </c>
       <c r="G6" s="7" t="s">
+        <v>361</v>
+      </c>
+      <c r="H6" s="7" t="s">
         <v>362</v>
       </c>
-      <c r="H6" s="7" t="s">
+      <c r="I6" s="7" t="s">
+        <v>364</v>
+      </c>
+      <c r="J6" s="8" t="s">
         <v>363</v>
-      </c>
-      <c r="I6" s="7" t="s">
-        <v>365</v>
-      </c>
-      <c r="J6" s="8" t="s">
-        <v>364</v>
       </c>
       <c r="M6" t="b">
         <v>0</v>
@@ -2686,58 +2780,70 @@
         <v>C:\Users\loyola\OneDrive - World Wildlife Fund, Inc\Documents\203. Python projects\SBTN_Test\data\crops\FAO_GAEZ\YIELDS\GAEZ-V5.RES06-YLD.COF.WSI.tif</v>
       </c>
       <c r="Q6" s="5" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="R6" s="5" t="s">
+        <v>425</v>
+      </c>
+      <c r="S6" s="6" t="s">
         <v>426</v>
-      </c>
-      <c r="S6" s="6" t="s">
-        <v>427</v>
       </c>
       <c r="T6" t="b">
         <v>0</v>
       </c>
       <c r="U6" s="11" t="s">
+        <v>547</v>
+      </c>
+      <c r="V6" t="s">
         <v>548</v>
       </c>
-      <c r="V6" t="s">
+      <c r="W6" t="s">
         <v>549</v>
       </c>
-      <c r="W6" t="s">
-        <v>550</v>
-      </c>
-    </row>
-    <row r="7" spans="1:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="X6" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y6" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z6">
+        <v>99.5</v>
+      </c>
+      <c r="AC6">
+        <v>99.5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:29" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B7" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C7" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D7" s="2">
         <v>14</v>
       </c>
       <c r="E7" t="s">
-        <v>6</v>
+        <v>550</v>
       </c>
       <c r="F7" t="str">
         <f t="shared" si="0"/>
         <v>RothC model results for year 2030 for Grapes, irrigated</v>
       </c>
       <c r="G7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H7" t="s">
+        <v>335</v>
+      </c>
+      <c r="I7" t="s">
         <v>336</v>
       </c>
-      <c r="I7" t="s">
+      <c r="J7" t="s">
         <v>337</v>
-      </c>
-      <c r="J7" t="s">
-        <v>338</v>
       </c>
       <c r="M7" t="b">
         <v>0</v>
@@ -2753,58 +2859,70 @@
         <v>C:\Users\loyola\OneDrive - World Wildlife Fund, Inc\Documents\203. Python projects\SBTN_Test\data\crops\FAO_GAEZ\YIELDS\GAEZ-V5.RES06-YLD.FRT.WSI.tif</v>
       </c>
       <c r="Q7" s="7" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="R7" s="7" t="s">
+        <v>443</v>
+      </c>
+      <c r="S7" s="8" t="s">
         <v>444</v>
-      </c>
-      <c r="S7" s="8" t="s">
-        <v>445</v>
       </c>
       <c r="T7" t="b">
         <v>0</v>
       </c>
       <c r="U7" s="11" t="s">
+        <v>547</v>
+      </c>
+      <c r="V7" t="s">
         <v>548</v>
       </c>
-      <c r="V7" t="s">
+      <c r="W7" t="s">
         <v>549</v>
       </c>
-      <c r="W7" t="s">
-        <v>550</v>
-      </c>
-    </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="X7" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y7" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z7">
+        <v>99.5</v>
+      </c>
+      <c r="AC7">
+        <v>99.5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B8" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C8" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D8" s="2">
         <v>14</v>
       </c>
       <c r="E8" t="s">
-        <v>6</v>
+        <v>550</v>
       </c>
       <c r="F8" t="str">
         <f t="shared" si="0"/>
         <v>RothC model results for year 2030 for Oil palm, irrigated</v>
       </c>
       <c r="G8" s="5" t="s">
+        <v>365</v>
+      </c>
+      <c r="H8" s="5" t="s">
         <v>366</v>
       </c>
-      <c r="H8" s="5" t="s">
+      <c r="I8" s="5" t="s">
+        <v>368</v>
+      </c>
+      <c r="J8" s="6" t="s">
         <v>367</v>
-      </c>
-      <c r="I8" s="5" t="s">
-        <v>369</v>
-      </c>
-      <c r="J8" s="6" t="s">
-        <v>368</v>
       </c>
       <c r="M8" t="b">
         <v>0</v>
@@ -2820,58 +2938,70 @@
         <v>C:\Users\loyola\OneDrive - World Wildlife Fund, Inc\Documents\203. Python projects\SBTN_Test\data\crops\FAO_GAEZ\YIELDS\GAEZ-V5.RES06-YLD.OLP.WSI.tif</v>
       </c>
       <c r="Q8" s="7" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="R8" s="7" t="s">
+        <v>473</v>
+      </c>
+      <c r="S8" s="8" t="s">
         <v>474</v>
-      </c>
-      <c r="S8" s="8" t="s">
-        <v>475</v>
       </c>
       <c r="T8" t="b">
         <v>0</v>
       </c>
       <c r="U8" s="11" t="s">
+        <v>547</v>
+      </c>
+      <c r="V8" t="s">
         <v>548</v>
       </c>
-      <c r="V8" t="s">
+      <c r="W8" t="s">
         <v>549</v>
       </c>
-      <c r="W8" t="s">
-        <v>550</v>
-      </c>
-    </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="X8" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y8" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z8">
+        <v>99.5</v>
+      </c>
+      <c r="AC8">
+        <v>99.5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B9" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C9" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D9" s="2">
         <v>14</v>
       </c>
       <c r="E9" t="s">
-        <v>6</v>
+        <v>550</v>
       </c>
       <c r="F9" t="str">
         <f t="shared" si="0"/>
         <v>RothC model results for year 2030 for Olive, irrigated</v>
       </c>
       <c r="G9" s="7" t="s">
+        <v>369</v>
+      </c>
+      <c r="H9" s="7" t="s">
         <v>370</v>
       </c>
-      <c r="H9" s="7" t="s">
+      <c r="I9" s="7" t="s">
+        <v>372</v>
+      </c>
+      <c r="J9" s="8" t="s">
         <v>371</v>
-      </c>
-      <c r="I9" s="7" t="s">
-        <v>373</v>
-      </c>
-      <c r="J9" s="8" t="s">
-        <v>372</v>
       </c>
       <c r="M9" t="b">
         <v>0</v>
@@ -2887,58 +3017,70 @@
         <v>C:\Users\loyola\OneDrive - World Wildlife Fund, Inc\Documents\203. Python projects\SBTN_Test\data\crops\FAO_GAEZ\YIELDS\GAEZ-V5.RES06-YLD.OOC.WSI.tif</v>
       </c>
       <c r="Q9" s="5" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="R9" s="5" t="s">
+        <v>477</v>
+      </c>
+      <c r="S9" s="6" t="s">
         <v>478</v>
-      </c>
-      <c r="S9" s="6" t="s">
-        <v>479</v>
       </c>
       <c r="T9" t="b">
         <v>0</v>
       </c>
       <c r="U9" s="11" t="s">
+        <v>547</v>
+      </c>
+      <c r="V9" t="s">
         <v>548</v>
       </c>
-      <c r="V9" t="s">
+      <c r="W9" t="s">
         <v>549</v>
       </c>
-      <c r="W9" t="s">
-        <v>550</v>
-      </c>
-    </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="X9" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y9" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z9">
+        <v>99.5</v>
+      </c>
+      <c r="AC9">
+        <v>99.5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
+        <v>22</v>
+      </c>
+      <c r="B10" t="s">
+        <v>331</v>
+      </c>
+      <c r="C10" t="s">
         <v>23</v>
-      </c>
-      <c r="B10" t="s">
-        <v>332</v>
-      </c>
-      <c r="C10" t="s">
-        <v>24</v>
       </c>
       <c r="D10" s="2">
         <v>14</v>
       </c>
       <c r="E10" t="s">
-        <v>6</v>
+        <v>550</v>
       </c>
       <c r="F10" t="str">
         <f t="shared" si="0"/>
         <v>RothC model results for year 2030 for Orange, irrigated</v>
       </c>
       <c r="G10" s="5" t="s">
+        <v>373</v>
+      </c>
+      <c r="H10" s="5" t="s">
         <v>374</v>
       </c>
-      <c r="H10" s="5" t="s">
+      <c r="I10" s="5" t="s">
+        <v>376</v>
+      </c>
+      <c r="J10" s="6" t="s">
         <v>375</v>
-      </c>
-      <c r="I10" s="5" t="s">
-        <v>377</v>
-      </c>
-      <c r="J10" s="6" t="s">
-        <v>376</v>
       </c>
       <c r="M10" t="b">
         <v>0</v>
@@ -2954,55 +3096,67 @@
         <v>C:\Users\loyola\OneDrive - World Wildlife Fund, Inc\Documents\203. Python projects\SBTN_Test\data\crops\FAO_GAEZ\YIELDS\GAEZ-V5.RES06-YLD.FRT.WSI.tif</v>
       </c>
       <c r="Q10" s="7" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="R10" s="7" t="s">
+        <v>443</v>
+      </c>
+      <c r="S10" s="8" t="s">
         <v>444</v>
-      </c>
-      <c r="S10" s="8" t="s">
-        <v>445</v>
       </c>
       <c r="T10" t="b">
         <v>0</v>
       </c>
       <c r="U10" s="11" t="s">
+        <v>547</v>
+      </c>
+      <c r="V10" t="s">
         <v>548</v>
       </c>
-      <c r="V10" t="s">
+      <c r="W10" t="s">
         <v>549</v>
       </c>
-      <c r="W10" t="s">
-        <v>550</v>
-      </c>
-    </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="X10" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y10" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z10">
+        <v>99.5</v>
+      </c>
+      <c r="AC10">
+        <v>99.5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B11" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D11" s="2">
         <v>14</v>
       </c>
       <c r="E11" t="s">
-        <v>6</v>
+        <v>550</v>
       </c>
       <c r="F11" t="str">
         <f t="shared" si="0"/>
         <v>RothC model results for year 2030 for Apple, rainfed</v>
       </c>
       <c r="G11" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H11" t="s">
+        <v>338</v>
+      </c>
+      <c r="I11" t="s">
         <v>339</v>
-      </c>
-      <c r="I11" t="s">
-        <v>340</v>
       </c>
       <c r="M11" t="b">
         <v>0</v>
@@ -3018,55 +3172,67 @@
         <v>C:\Users\loyola\OneDrive - World Wildlife Fund, Inc\Documents\203. Python projects\SBTN_Test\data\crops\FAO_GAEZ\YIELDS\GAEZ-V5.RES06-YLD.FRT.WSR.tif</v>
       </c>
       <c r="Q11" s="7" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="R11" s="7" t="s">
+        <v>443</v>
+      </c>
+      <c r="S11" s="8" t="s">
         <v>444</v>
-      </c>
-      <c r="S11" s="8" t="s">
-        <v>445</v>
       </c>
       <c r="T11" t="b">
         <v>0</v>
       </c>
       <c r="U11" s="11" t="s">
+        <v>547</v>
+      </c>
+      <c r="V11" t="s">
         <v>548</v>
       </c>
-      <c r="V11" t="s">
+      <c r="W11" t="s">
         <v>549</v>
       </c>
-      <c r="W11" t="s">
-        <v>550</v>
-      </c>
-    </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="X11" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y11" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z11">
+        <v>99.5</v>
+      </c>
+      <c r="AC11">
+        <v>99.5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B12" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C12" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D12" s="2">
         <v>14</v>
       </c>
       <c r="E12" t="s">
-        <v>6</v>
+        <v>550</v>
       </c>
       <c r="F12" t="str">
         <f t="shared" si="0"/>
         <v>RothC model results for year 2030 for Banana, rainfed</v>
       </c>
       <c r="G12" s="7" t="s">
+        <v>377</v>
+      </c>
+      <c r="H12" s="7" t="s">
         <v>378</v>
       </c>
-      <c r="H12" s="7" t="s">
-        <v>379</v>
-      </c>
       <c r="I12" s="7" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="J12" s="8"/>
       <c r="M12" t="b">
@@ -3083,55 +3249,67 @@
         <v>C:\Users\loyola\OneDrive - World Wildlife Fund, Inc\Documents\203. Python projects\SBTN_Test\data\crops\FAO_GAEZ\YIELDS\GAEZ-V5.RES06-YLD.BAN.WSR.tif</v>
       </c>
       <c r="Q12" s="5" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="R12" s="5" t="s">
+        <v>412</v>
+      </c>
+      <c r="S12" s="6" t="s">
         <v>413</v>
-      </c>
-      <c r="S12" s="6" t="s">
-        <v>414</v>
       </c>
       <c r="T12" t="b">
         <v>1</v>
       </c>
       <c r="U12" s="11" t="s">
+        <v>547</v>
+      </c>
+      <c r="V12" t="s">
         <v>548</v>
       </c>
-      <c r="V12" t="s">
+      <c r="W12" t="s">
         <v>549</v>
       </c>
-      <c r="W12" t="s">
-        <v>550</v>
-      </c>
-    </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="X12" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y12" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z12">
+        <v>99.5</v>
+      </c>
+      <c r="AC12">
+        <v>99.5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B13" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C13" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D13" s="2">
         <v>14</v>
       </c>
       <c r="E13" t="s">
-        <v>6</v>
+        <v>550</v>
       </c>
       <c r="F13" t="str">
         <f t="shared" si="0"/>
         <v>RothC model results for year 2030 for Cocoa, rainfed</v>
       </c>
       <c r="G13" s="5" t="s">
+        <v>381</v>
+      </c>
+      <c r="H13" s="5" t="s">
         <v>382</v>
       </c>
-      <c r="H13" s="5" t="s">
+      <c r="I13" s="5" t="s">
         <v>383</v>
-      </c>
-      <c r="I13" s="5" t="s">
-        <v>384</v>
       </c>
       <c r="J13" s="6"/>
       <c r="M13" t="b">
@@ -3148,55 +3326,67 @@
         <v>C:\Users\loyola\OneDrive - World Wildlife Fund, Inc\Documents\203. Python projects\SBTN_Test\data\crops\FAO_GAEZ\YIELDS\GAEZ-V5.RES06-YLD.COC.WSR.tif</v>
       </c>
       <c r="Q13" s="7" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="R13" s="7" t="s">
+        <v>422</v>
+      </c>
+      <c r="S13" s="8" t="s">
         <v>423</v>
-      </c>
-      <c r="S13" s="8" t="s">
-        <v>424</v>
       </c>
       <c r="T13" t="b">
         <v>1</v>
       </c>
       <c r="U13" s="11" t="s">
+        <v>547</v>
+      </c>
+      <c r="V13" t="s">
         <v>548</v>
       </c>
-      <c r="V13" t="s">
+      <c r="W13" t="s">
         <v>549</v>
       </c>
-      <c r="W13" t="s">
-        <v>550</v>
-      </c>
-    </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="X13" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y13" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z13">
+        <v>99.5</v>
+      </c>
+      <c r="AC13">
+        <v>99.5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B14" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C14" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D14" s="2">
         <v>14</v>
       </c>
       <c r="E14" t="s">
-        <v>6</v>
+        <v>550</v>
       </c>
       <c r="F14" t="str">
         <f t="shared" si="0"/>
         <v>RothC model results for year 2030 for Coconut, rainfed</v>
       </c>
       <c r="G14" s="7" t="s">
+        <v>384</v>
+      </c>
+      <c r="H14" s="7" t="s">
         <v>385</v>
       </c>
-      <c r="H14" s="7" t="s">
+      <c r="I14" s="7" t="s">
         <v>386</v>
-      </c>
-      <c r="I14" s="7" t="s">
-        <v>387</v>
       </c>
       <c r="J14" s="8"/>
       <c r="M14" t="b">
@@ -3213,55 +3403,67 @@
         <v>C:\Users\loyola\OneDrive - World Wildlife Fund, Inc\Documents\203. Python projects\SBTN_Test\data\crops\FAO_GAEZ\YIELDS\GAEZ-V5.RES06-YLD.CON.WSR.tif</v>
       </c>
       <c r="Q14" s="7" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="R14" s="7" t="s">
+        <v>428</v>
+      </c>
+      <c r="S14" s="8" t="s">
         <v>429</v>
-      </c>
-      <c r="S14" s="8" t="s">
-        <v>430</v>
       </c>
       <c r="T14" t="b">
         <v>1</v>
       </c>
       <c r="U14" s="11" t="s">
+        <v>547</v>
+      </c>
+      <c r="V14" t="s">
         <v>548</v>
       </c>
-      <c r="V14" t="s">
+      <c r="W14" t="s">
         <v>549</v>
       </c>
-      <c r="W14" t="s">
-        <v>550</v>
-      </c>
-    </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="X14" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y14" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z14">
+        <v>99.5</v>
+      </c>
+      <c r="AC14">
+        <v>99.5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B15" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C15" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D15" s="2">
         <v>14</v>
       </c>
       <c r="E15" t="s">
-        <v>6</v>
+        <v>550</v>
       </c>
       <c r="F15" t="str">
         <f t="shared" si="0"/>
         <v>RothC model results for year 2030 for Coffee, rainfed</v>
       </c>
       <c r="G15" s="5" t="s">
+        <v>387</v>
+      </c>
+      <c r="H15" s="5" t="s">
         <v>388</v>
       </c>
-      <c r="H15" s="5" t="s">
+      <c r="I15" s="5" t="s">
         <v>389</v>
-      </c>
-      <c r="I15" s="5" t="s">
-        <v>390</v>
       </c>
       <c r="J15" s="6"/>
       <c r="M15" t="b">
@@ -3278,55 +3480,67 @@
         <v>C:\Users\loyola\OneDrive - World Wildlife Fund, Inc\Documents\203. Python projects\SBTN_Test\data\crops\FAO_GAEZ\YIELDS\GAEZ-V5.RES06-YLD.COF.WSR.tif</v>
       </c>
       <c r="Q15" s="5" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="R15" s="5" t="s">
+        <v>425</v>
+      </c>
+      <c r="S15" s="6" t="s">
         <v>426</v>
-      </c>
-      <c r="S15" s="6" t="s">
-        <v>427</v>
       </c>
       <c r="T15" t="b">
         <v>1</v>
       </c>
       <c r="U15" s="11" t="s">
+        <v>547</v>
+      </c>
+      <c r="V15" t="s">
         <v>548</v>
       </c>
-      <c r="V15" t="s">
+      <c r="W15" t="s">
         <v>549</v>
       </c>
-      <c r="W15" t="s">
-        <v>550</v>
-      </c>
-    </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="X15" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y15" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z15">
+        <v>99.5</v>
+      </c>
+      <c r="AC15">
+        <v>99.5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B16" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C16" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D16" s="2">
         <v>14</v>
       </c>
       <c r="E16" t="s">
-        <v>6</v>
+        <v>550</v>
       </c>
       <c r="F16" t="str">
         <f t="shared" si="0"/>
         <v>RothC model results for year 2030 for Grapes, rainfed</v>
       </c>
       <c r="G16" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H16" t="s">
+        <v>340</v>
+      </c>
+      <c r="I16" t="s">
         <v>341</v>
-      </c>
-      <c r="I16" t="s">
-        <v>342</v>
       </c>
       <c r="M16" t="b">
         <v>0</v>
@@ -3342,55 +3556,67 @@
         <v>C:\Users\loyola\OneDrive - World Wildlife Fund, Inc\Documents\203. Python projects\SBTN_Test\data\crops\FAO_GAEZ\YIELDS\GAEZ-V5.RES06-YLD.FRT.WSR.tif</v>
       </c>
       <c r="Q16" s="7" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="R16" s="7" t="s">
+        <v>443</v>
+      </c>
+      <c r="S16" s="8" t="s">
         <v>444</v>
-      </c>
-      <c r="S16" s="8" t="s">
-        <v>445</v>
       </c>
       <c r="T16" t="b">
         <v>1</v>
       </c>
       <c r="U16" s="11" t="s">
+        <v>547</v>
+      </c>
+      <c r="V16" t="s">
         <v>548</v>
       </c>
-      <c r="V16" t="s">
+      <c r="W16" t="s">
         <v>549</v>
       </c>
-      <c r="W16" t="s">
-        <v>550</v>
-      </c>
-    </row>
-    <row r="17" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="X16" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y16" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z16">
+        <v>99.5</v>
+      </c>
+      <c r="AC16">
+        <v>99.5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B17" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C17" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D17" s="2">
         <v>14</v>
       </c>
       <c r="E17" t="s">
-        <v>6</v>
+        <v>550</v>
       </c>
       <c r="F17" t="str">
         <f t="shared" si="0"/>
         <v>RothC model results for year 2030 for Oil palm, rainfed</v>
       </c>
       <c r="G17" s="7" t="s">
+        <v>390</v>
+      </c>
+      <c r="H17" s="7" t="s">
         <v>391</v>
       </c>
-      <c r="H17" s="7" t="s">
+      <c r="I17" s="7" t="s">
         <v>392</v>
-      </c>
-      <c r="I17" s="7" t="s">
-        <v>393</v>
       </c>
       <c r="J17" s="8"/>
       <c r="M17" t="b">
@@ -3407,55 +3633,67 @@
         <v>C:\Users\loyola\OneDrive - World Wildlife Fund, Inc\Documents\203. Python projects\SBTN_Test\data\crops\FAO_GAEZ\YIELDS\GAEZ-V5.RES06-YLD.OLP.WSR.tif</v>
       </c>
       <c r="Q17" s="7" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="R17" s="7" t="s">
+        <v>473</v>
+      </c>
+      <c r="S17" s="8" t="s">
         <v>474</v>
-      </c>
-      <c r="S17" s="8" t="s">
-        <v>475</v>
       </c>
       <c r="T17" t="b">
         <v>1</v>
       </c>
       <c r="U17" s="11" t="s">
+        <v>547</v>
+      </c>
+      <c r="V17" t="s">
         <v>548</v>
       </c>
-      <c r="V17" t="s">
+      <c r="W17" t="s">
         <v>549</v>
       </c>
-      <c r="W17" t="s">
-        <v>550</v>
-      </c>
-    </row>
-    <row r="18" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="X17" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y17" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z17">
+        <v>99.5</v>
+      </c>
+      <c r="AC17">
+        <v>99.5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B18" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C18" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D18" s="2">
         <v>14</v>
       </c>
       <c r="E18" t="s">
-        <v>6</v>
+        <v>550</v>
       </c>
       <c r="F18" t="str">
         <f t="shared" si="0"/>
         <v>RothC model results for year 2030 for Olive, rainfed</v>
       </c>
       <c r="G18" s="5" t="s">
+        <v>393</v>
+      </c>
+      <c r="H18" s="5" t="s">
         <v>394</v>
       </c>
-      <c r="H18" s="5" t="s">
+      <c r="I18" s="5" t="s">
         <v>395</v>
-      </c>
-      <c r="I18" s="5" t="s">
-        <v>396</v>
       </c>
       <c r="J18" s="6"/>
       <c r="M18" t="b">
@@ -3472,55 +3710,67 @@
         <v>C:\Users\loyola\OneDrive - World Wildlife Fund, Inc\Documents\203. Python projects\SBTN_Test\data\crops\FAO_GAEZ\YIELDS\GAEZ-V5.RES06-YLD.OOC.WSR.tif</v>
       </c>
       <c r="Q18" s="5" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="R18" s="5" t="s">
+        <v>477</v>
+      </c>
+      <c r="S18" s="6" t="s">
         <v>478</v>
-      </c>
-      <c r="S18" s="6" t="s">
-        <v>479</v>
       </c>
       <c r="T18" t="b">
         <v>1</v>
       </c>
       <c r="U18" s="11" t="s">
+        <v>547</v>
+      </c>
+      <c r="V18" t="s">
         <v>548</v>
       </c>
-      <c r="V18" t="s">
+      <c r="W18" t="s">
         <v>549</v>
       </c>
-      <c r="W18" t="s">
-        <v>550</v>
-      </c>
-    </row>
-    <row r="19" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="X18" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y18" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z18">
+        <v>99.5</v>
+      </c>
+      <c r="AC18">
+        <v>99.5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B19" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C19" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D19" s="2">
         <v>14</v>
       </c>
       <c r="E19" t="s">
-        <v>6</v>
+        <v>550</v>
       </c>
       <c r="F19" t="str">
         <f t="shared" si="0"/>
         <v>RothC model results for year 2030 for Orange, rainfed</v>
       </c>
       <c r="G19" s="7" t="s">
+        <v>396</v>
+      </c>
+      <c r="H19" s="7" t="s">
         <v>397</v>
       </c>
-      <c r="H19" s="7" t="s">
+      <c r="I19" s="7" t="s">
         <v>398</v>
-      </c>
-      <c r="I19" s="7" t="s">
-        <v>399</v>
       </c>
       <c r="J19" s="8"/>
       <c r="M19" t="b">
@@ -3537,58 +3787,70 @@
         <v>C:\Users\loyola\OneDrive - World Wildlife Fund, Inc\Documents\203. Python projects\SBTN_Test\data\crops\FAO_GAEZ\YIELDS\GAEZ-V5.RES06-YLD.FRT.WSR.tif</v>
       </c>
       <c r="Q19" s="7" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="R19" s="7" t="s">
+        <v>443</v>
+      </c>
+      <c r="S19" s="8" t="s">
         <v>444</v>
-      </c>
-      <c r="S19" s="8" t="s">
-        <v>445</v>
       </c>
       <c r="T19" t="b">
         <v>1</v>
       </c>
       <c r="U19" s="11" t="s">
+        <v>547</v>
+      </c>
+      <c r="V19" t="s">
         <v>548</v>
       </c>
-      <c r="V19" t="s">
+      <c r="W19" t="s">
         <v>549</v>
       </c>
-      <c r="W19" t="s">
-        <v>550</v>
-      </c>
-    </row>
-    <row r="20" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="X19" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y19" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z19">
+        <v>99.5</v>
+      </c>
+      <c r="AC19">
+        <v>99.5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B20" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C20" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D20" s="1">
         <v>14</v>
       </c>
       <c r="E20" t="s">
-        <v>6</v>
+        <v>550</v>
       </c>
       <c r="F20" t="str">
         <f t="shared" si="0"/>
         <v>RothC model results for year 2030 for Sugarcane, irrigated</v>
       </c>
       <c r="G20" s="5" t="s">
+        <v>399</v>
+      </c>
+      <c r="H20" s="5" t="s">
         <v>400</v>
       </c>
-      <c r="H20" s="5" t="s">
+      <c r="I20" s="5" t="s">
+        <v>402</v>
+      </c>
+      <c r="J20" s="6" t="s">
         <v>401</v>
-      </c>
-      <c r="I20" s="5" t="s">
-        <v>403</v>
-      </c>
-      <c r="J20" s="6" t="s">
-        <v>402</v>
       </c>
       <c r="M20" t="b">
         <v>0</v>
@@ -3604,55 +3866,67 @@
         <v>C:\Users\loyola\OneDrive - World Wildlife Fund, Inc\Documents\203. Python projects\SBTN_Test\data\crops\FAO_GAEZ\YIELDS\GAEZ-V5.RES06-YLD.SUC.WSI.tif</v>
       </c>
       <c r="Q20" s="5" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="R20" s="5" t="s">
+        <v>526</v>
+      </c>
+      <c r="S20" s="6" t="s">
         <v>527</v>
-      </c>
-      <c r="S20" s="6" t="s">
-        <v>528</v>
       </c>
       <c r="T20" t="b">
         <v>1</v>
       </c>
       <c r="U20" s="11" t="s">
+        <v>547</v>
+      </c>
+      <c r="V20" t="s">
         <v>548</v>
       </c>
-      <c r="V20" t="s">
+      <c r="W20" t="s">
         <v>549</v>
       </c>
-      <c r="W20" t="s">
-        <v>550</v>
-      </c>
-    </row>
-    <row r="21" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="X20" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y20" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z20">
+        <v>99.5</v>
+      </c>
+      <c r="AC20">
+        <v>99.5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B21" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C21" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D21" s="1">
         <v>14</v>
       </c>
       <c r="E21" t="s">
-        <v>6</v>
+        <v>550</v>
       </c>
       <c r="F21" t="str">
         <f t="shared" si="0"/>
         <v>RothC model results for year 2030 for Sugarcane, rainfed</v>
       </c>
       <c r="G21" s="7" t="s">
+        <v>403</v>
+      </c>
+      <c r="H21" s="7" t="s">
         <v>404</v>
       </c>
-      <c r="H21" s="7" t="s">
+      <c r="I21" s="7" t="s">
         <v>405</v>
-      </c>
-      <c r="I21" s="7" t="s">
-        <v>406</v>
       </c>
       <c r="J21" s="8"/>
       <c r="M21" t="b">
@@ -3669,25 +3943,37 @@
         <v>C:\Users\loyola\OneDrive - World Wildlife Fund, Inc\Documents\203. Python projects\SBTN_Test\data\crops\FAO_GAEZ\YIELDS\GAEZ-V5.RES06-YLD.SUC.WSR.tif</v>
       </c>
       <c r="Q21" s="5" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="R21" s="5" t="s">
+        <v>526</v>
+      </c>
+      <c r="S21" s="6" t="s">
         <v>527</v>
-      </c>
-      <c r="S21" s="6" t="s">
-        <v>528</v>
       </c>
       <c r="T21" t="b">
         <v>1</v>
       </c>
       <c r="U21" s="11" t="s">
+        <v>547</v>
+      </c>
+      <c r="V21" t="s">
         <v>548</v>
       </c>
-      <c r="V21" t="s">
+      <c r="W21" t="s">
         <v>549</v>
       </c>
-      <c r="W21" t="s">
-        <v>550</v>
+      <c r="X21" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y21" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z21">
+        <v>99.5</v>
+      </c>
+      <c r="AC21">
+        <v>99.5</v>
       </c>
     </row>
   </sheetData>
@@ -3707,534 +3993,534 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B1" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
+        <v>411</v>
+      </c>
+      <c r="B2" t="s">
+        <v>414</v>
+      </c>
+      <c r="C2" t="s">
         <v>412</v>
       </c>
-      <c r="B2" t="s">
-        <v>415</v>
-      </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>413</v>
-      </c>
-      <c r="D2" t="s">
-        <v>414</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B3" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="C3" t="s">
+        <v>415</v>
+      </c>
+      <c r="D3" t="s">
         <v>416</v>
-      </c>
-      <c r="D3" t="s">
-        <v>417</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
+        <v>418</v>
+      </c>
+      <c r="B4" t="s">
+        <v>421</v>
+      </c>
+      <c r="C4" t="s">
         <v>419</v>
       </c>
-      <c r="B4" t="s">
-        <v>422</v>
-      </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>420</v>
-      </c>
-      <c r="D4" t="s">
-        <v>421</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B5" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="C5" t="s">
+        <v>422</v>
+      </c>
+      <c r="D5" t="s">
         <v>423</v>
-      </c>
-      <c r="D5" t="s">
-        <v>424</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B6" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="C6" t="s">
+        <v>425</v>
+      </c>
+      <c r="D6" t="s">
         <v>426</v>
-      </c>
-      <c r="D6" t="s">
-        <v>427</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B7" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="C7" t="s">
+        <v>428</v>
+      </c>
+      <c r="D7" t="s">
         <v>429</v>
-      </c>
-      <c r="D7" t="s">
-        <v>430</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
+        <v>431</v>
+      </c>
+      <c r="B8" t="s">
+        <v>434</v>
+      </c>
+      <c r="C8" t="s">
         <v>432</v>
       </c>
-      <c r="B8" t="s">
-        <v>435</v>
-      </c>
-      <c r="C8" t="s">
+      <c r="D8" t="s">
         <v>433</v>
-      </c>
-      <c r="D8" t="s">
-        <v>434</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B9" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="C9" t="s">
+        <v>435</v>
+      </c>
+      <c r="D9" t="s">
         <v>436</v>
-      </c>
-      <c r="D9" t="s">
-        <v>437</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
+        <v>438</v>
+      </c>
+      <c r="B10" t="s">
+        <v>441</v>
+      </c>
+      <c r="C10" t="s">
         <v>439</v>
       </c>
-      <c r="B10" t="s">
-        <v>442</v>
-      </c>
-      <c r="C10" t="s">
+      <c r="D10" t="s">
         <v>440</v>
-      </c>
-      <c r="D10" t="s">
-        <v>441</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
+        <v>442</v>
+      </c>
+      <c r="B11" t="s">
+        <v>445</v>
+      </c>
+      <c r="C11" t="s">
         <v>443</v>
       </c>
-      <c r="B11" t="s">
-        <v>446</v>
-      </c>
-      <c r="C11" t="s">
+      <c r="D11" t="s">
         <v>444</v>
-      </c>
-      <c r="D11" t="s">
-        <v>445</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
+        <v>446</v>
+      </c>
+      <c r="B12" t="s">
+        <v>449</v>
+      </c>
+      <c r="C12" t="s">
         <v>447</v>
       </c>
-      <c r="B12" t="s">
-        <v>450</v>
-      </c>
-      <c r="C12" t="s">
+      <c r="D12" t="s">
         <v>448</v>
-      </c>
-      <c r="D12" t="s">
-        <v>449</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
+        <v>450</v>
+      </c>
+      <c r="B13" t="s">
+        <v>453</v>
+      </c>
+      <c r="C13" t="s">
         <v>451</v>
       </c>
-      <c r="B13" t="s">
-        <v>454</v>
-      </c>
-      <c r="C13" t="s">
+      <c r="D13" t="s">
         <v>452</v>
-      </c>
-      <c r="D13" t="s">
-        <v>453</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
+        <v>454</v>
+      </c>
+      <c r="B14" t="s">
+        <v>457</v>
+      </c>
+      <c r="C14" t="s">
         <v>455</v>
       </c>
-      <c r="B14" t="s">
-        <v>458</v>
-      </c>
-      <c r="C14" t="s">
+      <c r="D14" t="s">
         <v>456</v>
-      </c>
-      <c r="D14" t="s">
-        <v>457</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B15" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="C15" t="s">
+        <v>458</v>
+      </c>
+      <c r="D15" t="s">
         <v>459</v>
-      </c>
-      <c r="D15" t="s">
-        <v>460</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
+        <v>461</v>
+      </c>
+      <c r="B16" t="s">
+        <v>464</v>
+      </c>
+      <c r="C16" t="s">
         <v>462</v>
       </c>
-      <c r="B16" t="s">
-        <v>465</v>
-      </c>
-      <c r="C16" t="s">
+      <c r="D16" t="s">
         <v>463</v>
-      </c>
-      <c r="D16" t="s">
-        <v>464</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
+        <v>465</v>
+      </c>
+      <c r="B17" t="s">
+        <v>468</v>
+      </c>
+      <c r="C17" t="s">
         <v>466</v>
       </c>
-      <c r="B17" t="s">
-        <v>469</v>
-      </c>
-      <c r="C17" t="s">
+      <c r="D17" t="s">
         <v>467</v>
-      </c>
-      <c r="D17" t="s">
-        <v>468</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
+        <v>469</v>
+      </c>
+      <c r="B18" t="s">
+        <v>472</v>
+      </c>
+      <c r="C18" t="s">
         <v>470</v>
       </c>
-      <c r="B18" t="s">
-        <v>473</v>
-      </c>
-      <c r="C18" t="s">
+      <c r="D18" t="s">
         <v>471</v>
-      </c>
-      <c r="D18" t="s">
-        <v>472</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B19" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="C19" t="s">
+        <v>473</v>
+      </c>
+      <c r="D19" t="s">
         <v>474</v>
-      </c>
-      <c r="D19" t="s">
-        <v>475</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
+        <v>476</v>
+      </c>
+      <c r="B20" t="s">
+        <v>479</v>
+      </c>
+      <c r="C20" t="s">
         <v>477</v>
       </c>
-      <c r="B20" t="s">
-        <v>480</v>
-      </c>
-      <c r="C20" t="s">
+      <c r="D20" t="s">
         <v>478</v>
-      </c>
-      <c r="D20" t="s">
-        <v>479</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
+        <v>480</v>
+      </c>
+      <c r="B21" t="s">
+        <v>483</v>
+      </c>
+      <c r="C21" t="s">
         <v>481</v>
       </c>
-      <c r="B21" t="s">
-        <v>484</v>
-      </c>
-      <c r="C21" t="s">
+      <c r="D21" t="s">
         <v>482</v>
-      </c>
-      <c r="D21" t="s">
-        <v>483</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
+        <v>484</v>
+      </c>
+      <c r="B22" t="s">
+        <v>487</v>
+      </c>
+      <c r="C22" t="s">
         <v>485</v>
       </c>
-      <c r="B22" t="s">
-        <v>488</v>
-      </c>
-      <c r="C22" t="s">
+      <c r="D22" t="s">
         <v>486</v>
-      </c>
-      <c r="D22" t="s">
-        <v>487</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
+        <v>488</v>
+      </c>
+      <c r="B23" t="s">
+        <v>491</v>
+      </c>
+      <c r="C23" t="s">
         <v>489</v>
       </c>
-      <c r="B23" t="s">
-        <v>492</v>
-      </c>
-      <c r="C23" t="s">
+      <c r="D23" t="s">
         <v>490</v>
-      </c>
-      <c r="D23" t="s">
-        <v>491</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
+        <v>492</v>
+      </c>
+      <c r="B24" t="s">
+        <v>495</v>
+      </c>
+      <c r="C24" t="s">
         <v>493</v>
       </c>
-      <c r="B24" t="s">
-        <v>496</v>
-      </c>
-      <c r="C24" t="s">
+      <c r="D24" t="s">
         <v>494</v>
-      </c>
-      <c r="D24" t="s">
-        <v>495</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B25" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="C25" t="s">
+        <v>496</v>
+      </c>
+      <c r="D25" t="s">
         <v>497</v>
-      </c>
-      <c r="D25" t="s">
-        <v>498</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B26" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="C26" t="s">
+        <v>499</v>
+      </c>
+      <c r="D26" t="s">
         <v>500</v>
-      </c>
-      <c r="D26" t="s">
-        <v>501</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
+        <v>502</v>
+      </c>
+      <c r="B27" t="s">
+        <v>505</v>
+      </c>
+      <c r="C27" t="s">
         <v>503</v>
       </c>
-      <c r="B27" t="s">
-        <v>506</v>
-      </c>
-      <c r="C27" t="s">
+      <c r="D27" t="s">
         <v>504</v>
-      </c>
-      <c r="D27" t="s">
-        <v>505</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
+        <v>506</v>
+      </c>
+      <c r="B28" t="s">
+        <v>509</v>
+      </c>
+      <c r="C28" t="s">
         <v>507</v>
       </c>
-      <c r="B28" t="s">
-        <v>510</v>
-      </c>
-      <c r="C28" t="s">
+      <c r="D28" t="s">
         <v>508</v>
-      </c>
-      <c r="D28" t="s">
-        <v>509</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
+        <v>510</v>
+      </c>
+      <c r="B29" t="s">
+        <v>513</v>
+      </c>
+      <c r="C29" t="s">
         <v>511</v>
       </c>
-      <c r="B29" t="s">
-        <v>514</v>
-      </c>
-      <c r="C29" t="s">
+      <c r="D29" t="s">
         <v>512</v>
-      </c>
-      <c r="D29" t="s">
-        <v>513</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B30" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="C30" t="s">
+        <v>514</v>
+      </c>
+      <c r="D30" t="s">
         <v>515</v>
-      </c>
-      <c r="D30" t="s">
-        <v>516</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B31" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="C31" t="s">
+        <v>517</v>
+      </c>
+      <c r="D31" t="s">
         <v>518</v>
-      </c>
-      <c r="D31" t="s">
-        <v>519</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B32" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="C32" t="s">
+        <v>520</v>
+      </c>
+      <c r="D32" t="s">
         <v>521</v>
-      </c>
-      <c r="D32" t="s">
-        <v>522</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B33" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="C33" t="s">
+        <v>523</v>
+      </c>
+      <c r="D33" t="s">
         <v>524</v>
-      </c>
-      <c r="D33" t="s">
-        <v>525</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B34" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="C34" t="s">
+        <v>526</v>
+      </c>
+      <c r="D34" t="s">
         <v>527</v>
-      </c>
-      <c r="D34" t="s">
-        <v>528</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
+        <v>529</v>
+      </c>
+      <c r="B35" t="s">
+        <v>532</v>
+      </c>
+      <c r="C35" t="s">
         <v>530</v>
       </c>
-      <c r="B35" t="s">
-        <v>533</v>
-      </c>
-      <c r="C35" t="s">
+      <c r="D35" t="s">
         <v>531</v>
-      </c>
-      <c r="D35" t="s">
-        <v>532</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
+        <v>533</v>
+      </c>
+      <c r="B36" t="s">
+        <v>536</v>
+      </c>
+      <c r="C36" t="s">
         <v>534</v>
       </c>
-      <c r="B36" t="s">
-        <v>537</v>
-      </c>
-      <c r="C36" t="s">
+      <c r="D36" t="s">
         <v>535</v>
-      </c>
-      <c r="D36" t="s">
-        <v>536</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B37" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="C37" t="s">
+        <v>537</v>
+      </c>
+      <c r="D37" t="s">
         <v>538</v>
-      </c>
-      <c r="D37" t="s">
-        <v>539</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B38" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="C38" t="s">
+        <v>540</v>
+      </c>
+      <c r="D38" t="s">
         <v>541</v>
-      </c>
-      <c r="D38" t="s">
-        <v>542</v>
       </c>
     </row>
   </sheetData>
@@ -4258,393 +4544,393 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B1" t="s">
+        <v>342</v>
+      </c>
+      <c r="C1" t="s">
         <v>343</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>344</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>345</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
+        <v>347</v>
+      </c>
+      <c r="G1" t="s">
         <v>346</v>
-      </c>
-      <c r="F1" t="s">
-        <v>348</v>
-      </c>
-      <c r="G1" t="s">
-        <v>347</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B2" t="s">
+        <v>348</v>
+      </c>
+      <c r="C2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2" t="s">
         <v>349</v>
       </c>
-      <c r="C2" t="s">
-        <v>24</v>
-      </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>350</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
+        <v>352</v>
+      </c>
+      <c r="G2" t="s">
         <v>351</v>
-      </c>
-      <c r="F2" t="s">
-        <v>353</v>
-      </c>
-      <c r="G2" t="s">
-        <v>352</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B3" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="C3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D3" t="s">
+        <v>353</v>
+      </c>
+      <c r="E3" t="s">
         <v>354</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
+        <v>356</v>
+      </c>
+      <c r="G3" t="s">
         <v>355</v>
-      </c>
-      <c r="F3" t="s">
-        <v>357</v>
-      </c>
-      <c r="G3" t="s">
-        <v>356</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B4" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="C4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D4" t="s">
+        <v>357</v>
+      </c>
+      <c r="E4" t="s">
         <v>358</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
+        <v>360</v>
+      </c>
+      <c r="G4" t="s">
         <v>359</v>
-      </c>
-      <c r="F4" t="s">
-        <v>361</v>
-      </c>
-      <c r="G4" t="s">
-        <v>360</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B5" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="C5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D5" t="s">
+        <v>361</v>
+      </c>
+      <c r="E5" t="s">
         <v>362</v>
       </c>
-      <c r="E5" t="s">
+      <c r="F5" t="s">
+        <v>364</v>
+      </c>
+      <c r="G5" t="s">
         <v>363</v>
-      </c>
-      <c r="F5" t="s">
-        <v>365</v>
-      </c>
-      <c r="G5" t="s">
-        <v>364</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B6" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="C6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D6" t="s">
+        <v>365</v>
+      </c>
+      <c r="E6" t="s">
         <v>366</v>
       </c>
-      <c r="E6" t="s">
+      <c r="F6" t="s">
+        <v>368</v>
+      </c>
+      <c r="G6" t="s">
         <v>367</v>
-      </c>
-      <c r="F6" t="s">
-        <v>369</v>
-      </c>
-      <c r="G6" t="s">
-        <v>368</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B7" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="C7" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D7" t="s">
+        <v>369</v>
+      </c>
+      <c r="E7" t="s">
         <v>370</v>
       </c>
-      <c r="E7" t="s">
+      <c r="F7" t="s">
+        <v>372</v>
+      </c>
+      <c r="G7" t="s">
         <v>371</v>
-      </c>
-      <c r="F7" t="s">
-        <v>373</v>
-      </c>
-      <c r="G7" t="s">
-        <v>372</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" t="s">
+        <v>348</v>
+      </c>
+      <c r="C8" t="s">
         <v>23</v>
       </c>
-      <c r="B8" t="s">
-        <v>349</v>
-      </c>
-      <c r="C8" t="s">
-        <v>24</v>
-      </c>
       <c r="D8" t="s">
+        <v>373</v>
+      </c>
+      <c r="E8" t="s">
         <v>374</v>
       </c>
-      <c r="E8" t="s">
+      <c r="F8" t="s">
+        <v>376</v>
+      </c>
+      <c r="G8" t="s">
         <v>375</v>
-      </c>
-      <c r="F8" t="s">
-        <v>377</v>
-      </c>
-      <c r="G8" t="s">
-        <v>376</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B9" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="C9" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D9" t="s">
+        <v>377</v>
+      </c>
+      <c r="E9" t="s">
         <v>378</v>
       </c>
-      <c r="E9" t="s">
+      <c r="F9" t="s">
+        <v>380</v>
+      </c>
+      <c r="G9" t="s">
         <v>379</v>
-      </c>
-      <c r="F9" t="s">
-        <v>381</v>
-      </c>
-      <c r="G9" t="s">
-        <v>380</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B10" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="C10" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D10" t="s">
+        <v>381</v>
+      </c>
+      <c r="E10" t="s">
         <v>382</v>
       </c>
-      <c r="E10" t="s">
+      <c r="F10" t="s">
         <v>383</v>
       </c>
-      <c r="F10" t="s">
-        <v>384</v>
-      </c>
       <c r="G10" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B11" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="C11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D11" t="s">
+        <v>384</v>
+      </c>
+      <c r="E11" t="s">
         <v>385</v>
       </c>
-      <c r="E11" t="s">
+      <c r="F11" t="s">
         <v>386</v>
       </c>
-      <c r="F11" t="s">
-        <v>387</v>
-      </c>
       <c r="G11" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B12" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="C12" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D12" t="s">
+        <v>387</v>
+      </c>
+      <c r="E12" t="s">
         <v>388</v>
       </c>
-      <c r="E12" t="s">
+      <c r="F12" t="s">
         <v>389</v>
       </c>
-      <c r="F12" t="s">
-        <v>390</v>
-      </c>
       <c r="G12" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B13" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="C13" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D13" t="s">
+        <v>390</v>
+      </c>
+      <c r="E13" t="s">
         <v>391</v>
       </c>
-      <c r="E13" t="s">
+      <c r="F13" t="s">
         <v>392</v>
       </c>
-      <c r="F13" t="s">
-        <v>393</v>
-      </c>
       <c r="G13" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B14" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="C14" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D14" t="s">
+        <v>393</v>
+      </c>
+      <c r="E14" t="s">
         <v>394</v>
       </c>
-      <c r="E14" t="s">
+      <c r="F14" t="s">
         <v>395</v>
       </c>
-      <c r="F14" t="s">
-        <v>396</v>
-      </c>
       <c r="G14" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B15" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="C15" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D15" t="s">
+        <v>396</v>
+      </c>
+      <c r="E15" t="s">
         <v>397</v>
       </c>
-      <c r="E15" t="s">
+      <c r="F15" t="s">
         <v>398</v>
       </c>
-      <c r="F15" t="s">
-        <v>399</v>
-      </c>
       <c r="G15" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B16" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="C16" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D16" t="s">
+        <v>399</v>
+      </c>
+      <c r="E16" t="s">
         <v>400</v>
       </c>
-      <c r="E16" t="s">
+      <c r="F16" t="s">
+        <v>402</v>
+      </c>
+      <c r="G16" t="s">
         <v>401</v>
-      </c>
-      <c r="F16" t="s">
-        <v>403</v>
-      </c>
-      <c r="G16" t="s">
-        <v>402</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B17" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="C17" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D17" t="s">
+        <v>403</v>
+      </c>
+      <c r="E17" t="s">
         <v>404</v>
       </c>
-      <c r="E17" t="s">
+      <c r="F17" t="s">
         <v>405</v>
       </c>
-      <c r="F17" t="s">
-        <v>406</v>
-      </c>
       <c r="G17" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
   </sheetData>
@@ -4666,495 +4952,495 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="C1" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="D1" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="E1" s="4" t="s">
         <v>34</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C2" t="s">
         <v>36</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>37</v>
       </c>
-      <c r="D2" t="s">
-        <v>38</v>
-      </c>
       <c r="E2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C3" t="s">
         <v>39</v>
       </c>
-      <c r="C3" t="s">
-        <v>40</v>
-      </c>
       <c r="D3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B4" t="s">
+        <v>40</v>
+      </c>
+      <c r="C4" t="s">
         <v>41</v>
       </c>
-      <c r="B4" t="s">
-        <v>41</v>
-      </c>
-      <c r="C4" t="s">
-        <v>42</v>
-      </c>
       <c r="D4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B5" t="s">
         <v>43</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
         <v>44</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" t="s">
         <v>45</v>
       </c>
-      <c r="D5" t="s">
-        <v>46</v>
-      </c>
       <c r="E5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
+        <v>46</v>
+      </c>
+      <c r="B6" t="s">
         <v>47</v>
       </c>
-      <c r="B6" t="s">
+      <c r="C6" t="s">
         <v>48</v>
       </c>
-      <c r="C6" t="s">
+      <c r="D6" t="s">
         <v>49</v>
       </c>
-      <c r="D6" t="s">
-        <v>50</v>
-      </c>
       <c r="E6" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B7" t="s">
+        <v>50</v>
+      </c>
+      <c r="C7" t="s">
         <v>51</v>
       </c>
-      <c r="C7" t="s">
-        <v>52</v>
-      </c>
       <c r="D7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B8" t="s">
+        <v>52</v>
+      </c>
+      <c r="C8" t="s">
         <v>53</v>
       </c>
-      <c r="C8" t="s">
-        <v>54</v>
-      </c>
       <c r="D8" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E8" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B9" t="s">
+        <v>54</v>
+      </c>
+      <c r="C9" t="s">
         <v>55</v>
       </c>
-      <c r="C9" t="s">
+      <c r="D9" t="s">
         <v>56</v>
       </c>
-      <c r="D9" t="s">
-        <v>57</v>
-      </c>
       <c r="E9" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
+        <v>57</v>
+      </c>
+      <c r="B10" t="s">
         <v>58</v>
       </c>
-      <c r="B10" t="s">
+      <c r="C10" t="s">
         <v>59</v>
       </c>
-      <c r="C10" t="s">
-        <v>60</v>
-      </c>
       <c r="D10" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E10" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B11" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C11" t="s">
+        <v>36</v>
+      </c>
+      <c r="D11" t="s">
         <v>37</v>
       </c>
-      <c r="D11" t="s">
-        <v>38</v>
-      </c>
       <c r="E11" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
+        <v>60</v>
+      </c>
+      <c r="B12" t="s">
         <v>61</v>
       </c>
-      <c r="B12" t="s">
+      <c r="C12" t="s">
         <v>62</v>
       </c>
-      <c r="C12" t="s">
+      <c r="D12" t="s">
+        <v>60</v>
+      </c>
+      <c r="E12" t="s">
         <v>63</v>
-      </c>
-      <c r="D12" t="s">
-        <v>61</v>
-      </c>
-      <c r="E12" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
+        <v>64</v>
+      </c>
+      <c r="B13" t="s">
         <v>65</v>
       </c>
-      <c r="B13" t="s">
+      <c r="C13" t="s">
         <v>66</v>
       </c>
-      <c r="C13" t="s">
-        <v>67</v>
-      </c>
       <c r="D13" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E13" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B14" t="s">
+        <v>67</v>
+      </c>
+      <c r="C14" t="s">
         <v>68</v>
       </c>
-      <c r="C14" t="s">
+      <c r="D14" t="s">
         <v>69</v>
       </c>
-      <c r="D14" t="s">
-        <v>70</v>
-      </c>
       <c r="E14" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B15" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C15" t="s">
+        <v>36</v>
+      </c>
+      <c r="D15" t="s">
         <v>37</v>
       </c>
-      <c r="D15" t="s">
-        <v>38</v>
-      </c>
       <c r="E15" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
+        <v>71</v>
+      </c>
+      <c r="B16" t="s">
         <v>72</v>
       </c>
-      <c r="B16" t="s">
+      <c r="C16" t="s">
         <v>73</v>
       </c>
-      <c r="C16" t="s">
-        <v>74</v>
-      </c>
       <c r="D16" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E16" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B17" t="s">
+        <v>74</v>
+      </c>
+      <c r="C17" t="s">
         <v>75</v>
       </c>
-      <c r="C17" t="s">
+      <c r="D17" t="s">
         <v>76</v>
       </c>
-      <c r="D17" t="s">
-        <v>77</v>
-      </c>
       <c r="E17" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
+        <v>77</v>
+      </c>
+      <c r="B18" t="s">
         <v>78</v>
       </c>
-      <c r="B18" t="s">
+      <c r="C18" t="s">
         <v>79</v>
       </c>
-      <c r="C18" t="s">
+      <c r="D18" t="s">
+        <v>77</v>
+      </c>
+      <c r="E18" t="s">
         <v>80</v>
-      </c>
-      <c r="D18" t="s">
-        <v>78</v>
-      </c>
-      <c r="E18" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
+        <v>81</v>
+      </c>
+      <c r="B19" t="s">
         <v>82</v>
       </c>
-      <c r="B19" t="s">
+      <c r="C19" t="s">
         <v>83</v>
       </c>
-      <c r="C19" t="s">
+      <c r="D19" t="s">
+        <v>81</v>
+      </c>
+      <c r="E19" t="s">
         <v>84</v>
-      </c>
-      <c r="D19" t="s">
-        <v>82</v>
-      </c>
-      <c r="E19" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
+        <v>85</v>
+      </c>
+      <c r="B20" t="s">
+        <v>85</v>
+      </c>
+      <c r="C20" t="s">
         <v>86</v>
       </c>
-      <c r="B20" t="s">
-        <v>86</v>
-      </c>
-      <c r="C20" t="s">
-        <v>87</v>
-      </c>
       <c r="D20" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E20" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
+        <v>87</v>
+      </c>
+      <c r="B21" t="s">
+        <v>87</v>
+      </c>
+      <c r="C21" t="s">
         <v>88</v>
       </c>
-      <c r="B21" t="s">
-        <v>88</v>
-      </c>
-      <c r="C21" t="s">
-        <v>89</v>
-      </c>
       <c r="D21" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E21" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
+        <v>89</v>
+      </c>
+      <c r="B22" t="s">
         <v>90</v>
       </c>
-      <c r="B22" t="s">
+      <c r="C22" t="s">
         <v>91</v>
       </c>
-      <c r="C22" t="s">
+      <c r="D22" t="s">
+        <v>89</v>
+      </c>
+      <c r="E22" t="s">
         <v>92</v>
-      </c>
-      <c r="D22" t="s">
-        <v>90</v>
-      </c>
-      <c r="E22" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
+        <v>93</v>
+      </c>
+      <c r="B23" t="s">
         <v>94</v>
       </c>
-      <c r="B23" t="s">
+      <c r="C23" t="s">
         <v>95</v>
       </c>
-      <c r="C23" t="s">
-        <v>96</v>
-      </c>
       <c r="D23" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E23" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
+        <v>96</v>
+      </c>
+      <c r="B24" t="s">
         <v>97</v>
       </c>
-      <c r="B24" t="s">
+      <c r="C24" t="s">
         <v>98</v>
       </c>
-      <c r="C24" t="s">
-        <v>99</v>
-      </c>
       <c r="D24" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E24" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
+        <v>99</v>
+      </c>
+      <c r="B25" t="s">
         <v>100</v>
       </c>
-      <c r="B25" t="s">
+      <c r="C25" t="s">
         <v>101</v>
       </c>
-      <c r="C25" t="s">
-        <v>102</v>
-      </c>
       <c r="D25" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E25" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
+        <v>102</v>
+      </c>
+      <c r="B26" t="s">
         <v>103</v>
       </c>
-      <c r="B26" t="s">
+      <c r="C26" t="s">
         <v>104</v>
       </c>
-      <c r="C26" t="s">
+      <c r="D26" t="s">
         <v>105</v>
       </c>
-      <c r="D26" t="s">
-        <v>106</v>
-      </c>
       <c r="E26" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
+        <v>106</v>
+      </c>
+      <c r="B27" t="s">
         <v>107</v>
       </c>
-      <c r="B27" t="s">
+      <c r="C27" t="s">
         <v>108</v>
       </c>
-      <c r="C27" t="s">
-        <v>109</v>
-      </c>
       <c r="D27" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E27" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
+        <v>109</v>
+      </c>
+      <c r="B28" t="s">
         <v>110</v>
       </c>
-      <c r="B28" t="s">
+      <c r="C28" t="s">
         <v>111</v>
       </c>
-      <c r="C28" t="s">
-        <v>112</v>
-      </c>
       <c r="D28" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E28" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
+        <v>112</v>
+      </c>
+      <c r="B29" t="s">
+        <v>112</v>
+      </c>
+      <c r="C29" t="s">
         <v>113</v>
       </c>
-      <c r="B29" t="s">
-        <v>113</v>
-      </c>
-      <c r="C29" t="s">
+      <c r="D29" t="s">
+        <v>112</v>
+      </c>
+      <c r="E29" t="s">
         <v>114</v>
-      </c>
-      <c r="D29" t="s">
-        <v>113</v>
-      </c>
-      <c r="E29" t="s">
-        <v>115</v>
       </c>
     </row>
   </sheetData>
@@ -5172,2782 +5458,2782 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B1" t="s">
         <v>116</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D1" t="s">
         <v>117</v>
       </c>
-      <c r="C1" t="s">
-        <v>34</v>
-      </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>118</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>119</v>
-      </c>
-      <c r="F1" t="s">
-        <v>120</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B2" t="s">
+        <v>121</v>
+      </c>
+      <c r="C2" t="s">
         <v>122</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" t="s">
         <v>123</v>
       </c>
-      <c r="D2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>124</v>
-      </c>
-      <c r="F2" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
+        <v>125</v>
+      </c>
+      <c r="B3" t="s">
+        <v>121</v>
+      </c>
+      <c r="C3" t="s">
+        <v>122</v>
+      </c>
+      <c r="D3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3" t="s">
         <v>126</v>
       </c>
-      <c r="B3" t="s">
-        <v>122</v>
-      </c>
-      <c r="C3" t="s">
-        <v>123</v>
-      </c>
-      <c r="D3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
         <v>127</v>
-      </c>
-      <c r="F3" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
+        <v>128</v>
+      </c>
+      <c r="B4" t="s">
+        <v>121</v>
+      </c>
+      <c r="C4" t="s">
+        <v>122</v>
+      </c>
+      <c r="D4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" t="s">
         <v>129</v>
       </c>
-      <c r="B4" t="s">
-        <v>122</v>
-      </c>
-      <c r="C4" t="s">
-        <v>123</v>
-      </c>
-      <c r="D4" t="s">
-        <v>16</v>
-      </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
         <v>130</v>
-      </c>
-      <c r="F4" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
+        <v>131</v>
+      </c>
+      <c r="B5" t="s">
+        <v>121</v>
+      </c>
+      <c r="C5" t="s">
         <v>132</v>
       </c>
-      <c r="B5" t="s">
-        <v>122</v>
-      </c>
-      <c r="C5" t="s">
-        <v>133</v>
-      </c>
       <c r="D5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E5" t="s">
+        <v>123</v>
+      </c>
+      <c r="F5" t="s">
         <v>124</v>
-      </c>
-      <c r="F5" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B6" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C6" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E6" t="s">
+        <v>126</v>
+      </c>
+      <c r="F6" t="s">
         <v>127</v>
-      </c>
-      <c r="F6" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B7" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C7" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E7" t="s">
+        <v>129</v>
+      </c>
+      <c r="F7" t="s">
         <v>130</v>
-      </c>
-      <c r="F7" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
+        <v>135</v>
+      </c>
+      <c r="B8" t="s">
+        <v>121</v>
+      </c>
+      <c r="C8" t="s">
         <v>136</v>
       </c>
-      <c r="B8" t="s">
-        <v>122</v>
-      </c>
-      <c r="C8" t="s">
+      <c r="D8" t="s">
         <v>137</v>
       </c>
-      <c r="D8" t="s">
-        <v>138</v>
-      </c>
       <c r="E8" t="s">
+        <v>123</v>
+      </c>
+      <c r="F8" t="s">
         <v>124</v>
-      </c>
-      <c r="F8" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B9" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C9" t="s">
+        <v>136</v>
+      </c>
+      <c r="D9" t="s">
         <v>137</v>
       </c>
-      <c r="D9" t="s">
-        <v>138</v>
-      </c>
       <c r="E9" t="s">
+        <v>126</v>
+      </c>
+      <c r="F9" t="s">
         <v>127</v>
-      </c>
-      <c r="F9" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B10" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C10" t="s">
+        <v>136</v>
+      </c>
+      <c r="D10" t="s">
         <v>137</v>
       </c>
-      <c r="D10" t="s">
-        <v>138</v>
-      </c>
       <c r="E10" t="s">
+        <v>129</v>
+      </c>
+      <c r="F10" t="s">
         <v>130</v>
-      </c>
-      <c r="F10" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
+        <v>140</v>
+      </c>
+      <c r="B11" t="s">
+        <v>121</v>
+      </c>
+      <c r="C11" t="s">
         <v>141</v>
       </c>
-      <c r="B11" t="s">
-        <v>122</v>
-      </c>
-      <c r="C11" t="s">
+      <c r="D11" t="s">
         <v>142</v>
       </c>
-      <c r="D11" t="s">
-        <v>143</v>
-      </c>
       <c r="E11" t="s">
+        <v>123</v>
+      </c>
+      <c r="F11" t="s">
         <v>124</v>
-      </c>
-      <c r="F11" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B12" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C12" t="s">
+        <v>141</v>
+      </c>
+      <c r="D12" t="s">
         <v>142</v>
       </c>
-      <c r="D12" t="s">
-        <v>143</v>
-      </c>
       <c r="E12" t="s">
+        <v>126</v>
+      </c>
+      <c r="F12" t="s">
         <v>127</v>
-      </c>
-      <c r="F12" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B13" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C13" t="s">
+        <v>141</v>
+      </c>
+      <c r="D13" t="s">
         <v>142</v>
       </c>
-      <c r="D13" t="s">
-        <v>143</v>
-      </c>
       <c r="E13" t="s">
+        <v>129</v>
+      </c>
+      <c r="F13" t="s">
         <v>130</v>
-      </c>
-      <c r="F13" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
+        <v>145</v>
+      </c>
+      <c r="B14" t="s">
+        <v>121</v>
+      </c>
+      <c r="C14" t="s">
         <v>146</v>
       </c>
-      <c r="B14" t="s">
-        <v>122</v>
-      </c>
-      <c r="C14" t="s">
+      <c r="D14" t="s">
         <v>147</v>
       </c>
-      <c r="D14" t="s">
-        <v>148</v>
-      </c>
       <c r="E14" t="s">
+        <v>123</v>
+      </c>
+      <c r="F14" t="s">
         <v>124</v>
-      </c>
-      <c r="F14" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B15" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C15" t="s">
+        <v>146</v>
+      </c>
+      <c r="D15" t="s">
         <v>147</v>
       </c>
-      <c r="D15" t="s">
-        <v>148</v>
-      </c>
       <c r="E15" t="s">
+        <v>126</v>
+      </c>
+      <c r="F15" t="s">
         <v>127</v>
-      </c>
-      <c r="F15" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B16" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C16" t="s">
+        <v>146</v>
+      </c>
+      <c r="D16" t="s">
         <v>147</v>
       </c>
-      <c r="D16" t="s">
-        <v>148</v>
-      </c>
       <c r="E16" t="s">
+        <v>129</v>
+      </c>
+      <c r="F16" t="s">
         <v>130</v>
-      </c>
-      <c r="F16" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
+        <v>150</v>
+      </c>
+      <c r="B17" t="s">
+        <v>121</v>
+      </c>
+      <c r="C17" t="s">
         <v>151</v>
       </c>
-      <c r="B17" t="s">
-        <v>122</v>
-      </c>
-      <c r="C17" t="s">
-        <v>152</v>
-      </c>
       <c r="D17" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E17" t="s">
+        <v>123</v>
+      </c>
+      <c r="F17" t="s">
         <v>124</v>
-      </c>
-      <c r="F17" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B18" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C18" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D18" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E18" t="s">
+        <v>126</v>
+      </c>
+      <c r="F18" t="s">
         <v>127</v>
-      </c>
-      <c r="F18" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B19" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C19" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D19" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E19" t="s">
+        <v>129</v>
+      </c>
+      <c r="F19" t="s">
         <v>130</v>
-      </c>
-      <c r="F19" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
+        <v>154</v>
+      </c>
+      <c r="B20" t="s">
+        <v>121</v>
+      </c>
+      <c r="C20" t="s">
         <v>155</v>
       </c>
-      <c r="B20" t="s">
-        <v>122</v>
-      </c>
-      <c r="C20" t="s">
-        <v>156</v>
-      </c>
       <c r="D20" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E20" t="s">
+        <v>123</v>
+      </c>
+      <c r="F20" t="s">
         <v>124</v>
-      </c>
-      <c r="F20" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B21" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C21" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D21" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E21" t="s">
+        <v>126</v>
+      </c>
+      <c r="F21" t="s">
         <v>127</v>
-      </c>
-      <c r="F21" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B22" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C22" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D22" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E22" t="s">
+        <v>129</v>
+      </c>
+      <c r="F22" t="s">
         <v>130</v>
-      </c>
-      <c r="F22" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
+        <v>158</v>
+      </c>
+      <c r="B23" t="s">
+        <v>121</v>
+      </c>
+      <c r="C23" t="s">
         <v>159</v>
       </c>
-      <c r="B23" t="s">
-        <v>122</v>
-      </c>
-      <c r="C23" t="s">
-        <v>160</v>
-      </c>
       <c r="D23" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E23" t="s">
+        <v>123</v>
+      </c>
+      <c r="F23" t="s">
         <v>124</v>
-      </c>
-      <c r="F23" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B24" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C24" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D24" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E24" t="s">
+        <v>126</v>
+      </c>
+      <c r="F24" t="s">
         <v>127</v>
-      </c>
-      <c r="F24" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B25" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C25" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D25" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E25" t="s">
+        <v>129</v>
+      </c>
+      <c r="F25" t="s">
         <v>130</v>
-      </c>
-      <c r="F25" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
+        <v>162</v>
+      </c>
+      <c r="B26" t="s">
+        <v>121</v>
+      </c>
+      <c r="C26" t="s">
         <v>163</v>
       </c>
-      <c r="B26" t="s">
-        <v>122</v>
-      </c>
-      <c r="C26" t="s">
-        <v>164</v>
-      </c>
       <c r="D26" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E26" t="s">
+        <v>123</v>
+      </c>
+      <c r="F26" t="s">
         <v>124</v>
-      </c>
-      <c r="F26" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B27" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C27" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D27" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E27" t="s">
+        <v>126</v>
+      </c>
+      <c r="F27" t="s">
         <v>127</v>
-      </c>
-      <c r="F27" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B28" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C28" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D28" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E28" t="s">
+        <v>129</v>
+      </c>
+      <c r="F28" t="s">
         <v>130</v>
-      </c>
-      <c r="F28" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
+        <v>166</v>
+      </c>
+      <c r="B29" t="s">
+        <v>121</v>
+      </c>
+      <c r="C29" t="s">
         <v>167</v>
       </c>
-      <c r="B29" t="s">
-        <v>122</v>
-      </c>
-      <c r="C29" t="s">
-        <v>168</v>
-      </c>
       <c r="D29" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E29" t="s">
+        <v>123</v>
+      </c>
+      <c r="F29" t="s">
         <v>124</v>
-      </c>
-      <c r="F29" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B30" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C30" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D30" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E30" t="s">
+        <v>126</v>
+      </c>
+      <c r="F30" t="s">
         <v>127</v>
-      </c>
-      <c r="F30" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B31" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C31" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D31" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E31" t="s">
+        <v>129</v>
+      </c>
+      <c r="F31" t="s">
         <v>130</v>
-      </c>
-      <c r="F31" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
+        <v>170</v>
+      </c>
+      <c r="B32" t="s">
+        <v>121</v>
+      </c>
+      <c r="C32" t="s">
         <v>171</v>
       </c>
-      <c r="B32" t="s">
-        <v>122</v>
-      </c>
-      <c r="C32" t="s">
+      <c r="D32" t="s">
         <v>172</v>
       </c>
-      <c r="D32" t="s">
-        <v>173</v>
-      </c>
       <c r="E32" t="s">
+        <v>123</v>
+      </c>
+      <c r="F32" t="s">
         <v>124</v>
-      </c>
-      <c r="F32" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B33" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C33" t="s">
+        <v>171</v>
+      </c>
+      <c r="D33" t="s">
         <v>172</v>
       </c>
-      <c r="D33" t="s">
-        <v>173</v>
-      </c>
       <c r="E33" t="s">
+        <v>126</v>
+      </c>
+      <c r="F33" t="s">
         <v>127</v>
-      </c>
-      <c r="F33" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B34" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C34" t="s">
+        <v>171</v>
+      </c>
+      <c r="D34" t="s">
         <v>172</v>
       </c>
-      <c r="D34" t="s">
-        <v>173</v>
-      </c>
       <c r="E34" t="s">
+        <v>129</v>
+      </c>
+      <c r="F34" t="s">
         <v>130</v>
-      </c>
-      <c r="F34" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
+        <v>175</v>
+      </c>
+      <c r="B35" t="s">
+        <v>121</v>
+      </c>
+      <c r="C35" t="s">
         <v>176</v>
       </c>
-      <c r="B35" t="s">
-        <v>122</v>
-      </c>
-      <c r="C35" t="s">
-        <v>177</v>
-      </c>
       <c r="D35" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E35" t="s">
+        <v>123</v>
+      </c>
+      <c r="F35" t="s">
         <v>124</v>
-      </c>
-      <c r="F35" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B36" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C36" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D36" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E36" t="s">
+        <v>126</v>
+      </c>
+      <c r="F36" t="s">
         <v>127</v>
-      </c>
-      <c r="F36" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B37" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C37" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D37" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E37" t="s">
+        <v>129</v>
+      </c>
+      <c r="F37" t="s">
         <v>130</v>
-      </c>
-      <c r="F37" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
+        <v>179</v>
+      </c>
+      <c r="B38" t="s">
+        <v>121</v>
+      </c>
+      <c r="C38" t="s">
         <v>180</v>
       </c>
-      <c r="B38" t="s">
-        <v>122</v>
-      </c>
-      <c r="C38" t="s">
+      <c r="D38" t="s">
         <v>181</v>
       </c>
-      <c r="D38" t="s">
-        <v>182</v>
-      </c>
       <c r="E38" t="s">
+        <v>123</v>
+      </c>
+      <c r="F38" t="s">
         <v>124</v>
-      </c>
-      <c r="F38" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B39" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C39" t="s">
+        <v>180</v>
+      </c>
+      <c r="D39" t="s">
         <v>181</v>
       </c>
-      <c r="D39" t="s">
-        <v>182</v>
-      </c>
       <c r="E39" t="s">
+        <v>126</v>
+      </c>
+      <c r="F39" t="s">
         <v>127</v>
-      </c>
-      <c r="F39" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B40" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C40" t="s">
+        <v>180</v>
+      </c>
+      <c r="D40" t="s">
         <v>181</v>
       </c>
-      <c r="D40" t="s">
-        <v>182</v>
-      </c>
       <c r="E40" t="s">
+        <v>129</v>
+      </c>
+      <c r="F40" t="s">
         <v>130</v>
-      </c>
-      <c r="F40" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
+        <v>184</v>
+      </c>
+      <c r="B41" t="s">
+        <v>121</v>
+      </c>
+      <c r="C41" t="s">
         <v>185</v>
       </c>
-      <c r="B41" t="s">
-        <v>122</v>
-      </c>
-      <c r="C41" t="s">
-        <v>186</v>
-      </c>
       <c r="D41" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E41" t="s">
+        <v>123</v>
+      </c>
+      <c r="F41" t="s">
         <v>124</v>
-      </c>
-      <c r="F41" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B42" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C42" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D42" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E42" t="s">
+        <v>126</v>
+      </c>
+      <c r="F42" t="s">
         <v>127</v>
-      </c>
-      <c r="F42" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B43" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C43" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D43" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E43" t="s">
+        <v>129</v>
+      </c>
+      <c r="F43" t="s">
         <v>130</v>
-      </c>
-      <c r="F43" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
+        <v>188</v>
+      </c>
+      <c r="B44" t="s">
+        <v>121</v>
+      </c>
+      <c r="C44" t="s">
         <v>189</v>
       </c>
-      <c r="B44" t="s">
-        <v>122</v>
-      </c>
-      <c r="C44" t="s">
+      <c r="D44" t="s">
         <v>190</v>
       </c>
-      <c r="D44" t="s">
-        <v>191</v>
-      </c>
       <c r="E44" t="s">
+        <v>123</v>
+      </c>
+      <c r="F44" t="s">
         <v>124</v>
-      </c>
-      <c r="F44" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B45" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C45" t="s">
+        <v>189</v>
+      </c>
+      <c r="D45" t="s">
         <v>190</v>
       </c>
-      <c r="D45" t="s">
-        <v>191</v>
-      </c>
       <c r="E45" t="s">
+        <v>126</v>
+      </c>
+      <c r="F45" t="s">
         <v>127</v>
-      </c>
-      <c r="F45" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B46" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C46" t="s">
+        <v>189</v>
+      </c>
+      <c r="D46" t="s">
         <v>190</v>
       </c>
-      <c r="D46" t="s">
-        <v>191</v>
-      </c>
       <c r="E46" t="s">
+        <v>129</v>
+      </c>
+      <c r="F46" t="s">
         <v>130</v>
-      </c>
-      <c r="F46" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
+        <v>193</v>
+      </c>
+      <c r="B47" t="s">
+        <v>121</v>
+      </c>
+      <c r="C47" t="s">
         <v>194</v>
       </c>
-      <c r="B47" t="s">
-        <v>122</v>
-      </c>
-      <c r="C47" t="s">
+      <c r="D47" t="s">
         <v>195</v>
       </c>
-      <c r="D47" t="s">
-        <v>196</v>
-      </c>
       <c r="E47" t="s">
+        <v>123</v>
+      </c>
+      <c r="F47" t="s">
         <v>124</v>
-      </c>
-      <c r="F47" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B48" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C48" t="s">
+        <v>194</v>
+      </c>
+      <c r="D48" t="s">
         <v>195</v>
       </c>
-      <c r="D48" t="s">
-        <v>196</v>
-      </c>
       <c r="E48" t="s">
+        <v>126</v>
+      </c>
+      <c r="F48" t="s">
         <v>127</v>
-      </c>
-      <c r="F48" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B49" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C49" t="s">
+        <v>194</v>
+      </c>
+      <c r="D49" t="s">
         <v>195</v>
       </c>
-      <c r="D49" t="s">
-        <v>196</v>
-      </c>
       <c r="E49" t="s">
+        <v>129</v>
+      </c>
+      <c r="F49" t="s">
         <v>130</v>
-      </c>
-      <c r="F49" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
+        <v>198</v>
+      </c>
+      <c r="B50" t="s">
+        <v>121</v>
+      </c>
+      <c r="C50" t="s">
         <v>199</v>
       </c>
-      <c r="B50" t="s">
-        <v>122</v>
-      </c>
-      <c r="C50" t="s">
+      <c r="D50" t="s">
         <v>200</v>
       </c>
-      <c r="D50" t="s">
-        <v>201</v>
-      </c>
       <c r="E50" t="s">
+        <v>123</v>
+      </c>
+      <c r="F50" t="s">
         <v>124</v>
-      </c>
-      <c r="F50" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B51" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C51" t="s">
+        <v>199</v>
+      </c>
+      <c r="D51" t="s">
         <v>200</v>
       </c>
-      <c r="D51" t="s">
-        <v>201</v>
-      </c>
       <c r="E51" t="s">
+        <v>126</v>
+      </c>
+      <c r="F51" t="s">
         <v>127</v>
-      </c>
-      <c r="F51" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B52" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C52" t="s">
+        <v>199</v>
+      </c>
+      <c r="D52" t="s">
         <v>200</v>
       </c>
-      <c r="D52" t="s">
-        <v>201</v>
-      </c>
       <c r="E52" t="s">
+        <v>129</v>
+      </c>
+      <c r="F52" t="s">
         <v>130</v>
-      </c>
-      <c r="F52" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
+        <v>203</v>
+      </c>
+      <c r="B53" t="s">
+        <v>121</v>
+      </c>
+      <c r="C53" t="s">
         <v>204</v>
       </c>
-      <c r="B53" t="s">
-        <v>122</v>
-      </c>
-      <c r="C53" t="s">
-        <v>205</v>
-      </c>
       <c r="D53" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E53" t="s">
+        <v>123</v>
+      </c>
+      <c r="F53" t="s">
         <v>124</v>
-      </c>
-      <c r="F53" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B54" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C54" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D54" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E54" t="s">
+        <v>126</v>
+      </c>
+      <c r="F54" t="s">
         <v>127</v>
-      </c>
-      <c r="F54" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B55" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C55" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D55" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E55" t="s">
+        <v>129</v>
+      </c>
+      <c r="F55" t="s">
         <v>130</v>
-      </c>
-      <c r="F55" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
+        <v>207</v>
+      </c>
+      <c r="B56" t="s">
+        <v>121</v>
+      </c>
+      <c r="C56" t="s">
         <v>208</v>
       </c>
-      <c r="B56" t="s">
-        <v>122</v>
-      </c>
-      <c r="C56" t="s">
-        <v>209</v>
-      </c>
       <c r="D56" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E56" t="s">
+        <v>123</v>
+      </c>
+      <c r="F56" t="s">
         <v>124</v>
-      </c>
-      <c r="F56" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B57" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C57" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="D57" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E57" t="s">
+        <v>126</v>
+      </c>
+      <c r="F57" t="s">
         <v>127</v>
-      </c>
-      <c r="F57" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B58" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C58" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="D58" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E58" t="s">
+        <v>129</v>
+      </c>
+      <c r="F58" t="s">
         <v>130</v>
-      </c>
-      <c r="F58" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
+        <v>211</v>
+      </c>
+      <c r="B59" t="s">
+        <v>121</v>
+      </c>
+      <c r="C59" t="s">
         <v>212</v>
       </c>
-      <c r="B59" t="s">
-        <v>122</v>
-      </c>
-      <c r="C59" t="s">
+      <c r="D59" t="s">
         <v>213</v>
       </c>
-      <c r="D59" t="s">
-        <v>214</v>
-      </c>
       <c r="E59" t="s">
+        <v>123</v>
+      </c>
+      <c r="F59" t="s">
         <v>124</v>
-      </c>
-      <c r="F59" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B60" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C60" t="s">
+        <v>212</v>
+      </c>
+      <c r="D60" t="s">
         <v>213</v>
       </c>
-      <c r="D60" t="s">
-        <v>214</v>
-      </c>
       <c r="E60" t="s">
+        <v>126</v>
+      </c>
+      <c r="F60" t="s">
         <v>127</v>
-      </c>
-      <c r="F60" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B61" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C61" t="s">
+        <v>212</v>
+      </c>
+      <c r="D61" t="s">
         <v>213</v>
       </c>
-      <c r="D61" t="s">
-        <v>214</v>
-      </c>
       <c r="E61" t="s">
+        <v>129</v>
+      </c>
+      <c r="F61" t="s">
         <v>130</v>
-      </c>
-      <c r="F61" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
+        <v>216</v>
+      </c>
+      <c r="B62" t="s">
+        <v>121</v>
+      </c>
+      <c r="C62" t="s">
         <v>217</v>
       </c>
-      <c r="B62" t="s">
-        <v>122</v>
-      </c>
-      <c r="C62" t="s">
+      <c r="D62" t="s">
         <v>218</v>
       </c>
-      <c r="D62" t="s">
-        <v>219</v>
-      </c>
       <c r="E62" t="s">
+        <v>123</v>
+      </c>
+      <c r="F62" t="s">
         <v>124</v>
-      </c>
-      <c r="F62" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B63" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C63" t="s">
+        <v>217</v>
+      </c>
+      <c r="D63" t="s">
         <v>218</v>
       </c>
-      <c r="D63" t="s">
-        <v>219</v>
-      </c>
       <c r="E63" t="s">
+        <v>126</v>
+      </c>
+      <c r="F63" t="s">
         <v>127</v>
-      </c>
-      <c r="F63" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B64" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C64" t="s">
+        <v>217</v>
+      </c>
+      <c r="D64" t="s">
         <v>218</v>
       </c>
-      <c r="D64" t="s">
-        <v>219</v>
-      </c>
       <c r="E64" t="s">
+        <v>129</v>
+      </c>
+      <c r="F64" t="s">
         <v>130</v>
-      </c>
-      <c r="F64" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
+        <v>221</v>
+      </c>
+      <c r="B65" t="s">
+        <v>121</v>
+      </c>
+      <c r="C65" t="s">
         <v>222</v>
       </c>
-      <c r="B65" t="s">
-        <v>122</v>
-      </c>
-      <c r="C65" t="s">
-        <v>223</v>
-      </c>
       <c r="D65" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E65" t="s">
+        <v>123</v>
+      </c>
+      <c r="F65" t="s">
         <v>124</v>
-      </c>
-      <c r="F65" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B66" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C66" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="D66" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E66" t="s">
+        <v>126</v>
+      </c>
+      <c r="F66" t="s">
         <v>127</v>
-      </c>
-      <c r="F66" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B67" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C67" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="D67" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E67" t="s">
+        <v>129</v>
+      </c>
+      <c r="F67" t="s">
         <v>130</v>
-      </c>
-      <c r="F67" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
+        <v>225</v>
+      </c>
+      <c r="B68" t="s">
+        <v>121</v>
+      </c>
+      <c r="C68" t="s">
         <v>226</v>
       </c>
-      <c r="B68" t="s">
-        <v>122</v>
-      </c>
-      <c r="C68" t="s">
+      <c r="D68" t="s">
         <v>227</v>
       </c>
-      <c r="D68" t="s">
-        <v>228</v>
-      </c>
       <c r="E68" t="s">
+        <v>123</v>
+      </c>
+      <c r="F68" t="s">
         <v>124</v>
-      </c>
-      <c r="F68" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B69" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C69" t="s">
+        <v>226</v>
+      </c>
+      <c r="D69" t="s">
         <v>227</v>
       </c>
-      <c r="D69" t="s">
-        <v>228</v>
-      </c>
       <c r="E69" t="s">
+        <v>126</v>
+      </c>
+      <c r="F69" t="s">
         <v>127</v>
-      </c>
-      <c r="F69" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B70" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C70" t="s">
+        <v>226</v>
+      </c>
+      <c r="D70" t="s">
         <v>227</v>
       </c>
-      <c r="D70" t="s">
-        <v>228</v>
-      </c>
       <c r="E70" t="s">
+        <v>129</v>
+      </c>
+      <c r="F70" t="s">
         <v>130</v>
-      </c>
-      <c r="F70" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
+        <v>230</v>
+      </c>
+      <c r="B71" t="s">
+        <v>121</v>
+      </c>
+      <c r="C71" t="s">
         <v>231</v>
       </c>
-      <c r="B71" t="s">
-        <v>122</v>
-      </c>
-      <c r="C71" t="s">
+      <c r="D71" t="s">
         <v>232</v>
       </c>
-      <c r="D71" t="s">
-        <v>233</v>
-      </c>
       <c r="E71" t="s">
+        <v>123</v>
+      </c>
+      <c r="F71" t="s">
         <v>124</v>
-      </c>
-      <c r="F71" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B72" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C72" t="s">
+        <v>231</v>
+      </c>
+      <c r="D72" t="s">
         <v>232</v>
       </c>
-      <c r="D72" t="s">
-        <v>233</v>
-      </c>
       <c r="E72" t="s">
+        <v>126</v>
+      </c>
+      <c r="F72" t="s">
         <v>127</v>
-      </c>
-      <c r="F72" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B73" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C73" t="s">
+        <v>231</v>
+      </c>
+      <c r="D73" t="s">
         <v>232</v>
       </c>
-      <c r="D73" t="s">
-        <v>233</v>
-      </c>
       <c r="E73" t="s">
+        <v>129</v>
+      </c>
+      <c r="F73" t="s">
         <v>130</v>
-      </c>
-      <c r="F73" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
+        <v>235</v>
+      </c>
+      <c r="B74" t="s">
+        <v>121</v>
+      </c>
+      <c r="C74" t="s">
         <v>236</v>
       </c>
-      <c r="B74" t="s">
-        <v>122</v>
-      </c>
-      <c r="C74" t="s">
+      <c r="D74" t="s">
         <v>237</v>
       </c>
-      <c r="D74" t="s">
-        <v>238</v>
-      </c>
       <c r="E74" t="s">
+        <v>123</v>
+      </c>
+      <c r="F74" t="s">
         <v>124</v>
-      </c>
-      <c r="F74" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B75" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C75" t="s">
+        <v>236</v>
+      </c>
+      <c r="D75" t="s">
         <v>237</v>
       </c>
-      <c r="D75" t="s">
-        <v>238</v>
-      </c>
       <c r="E75" t="s">
+        <v>126</v>
+      </c>
+      <c r="F75" t="s">
         <v>127</v>
-      </c>
-      <c r="F75" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B76" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C76" t="s">
+        <v>236</v>
+      </c>
+      <c r="D76" t="s">
         <v>237</v>
       </c>
-      <c r="D76" t="s">
-        <v>238</v>
-      </c>
       <c r="E76" t="s">
+        <v>129</v>
+      </c>
+      <c r="F76" t="s">
         <v>130</v>
-      </c>
-      <c r="F76" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
+        <v>240</v>
+      </c>
+      <c r="B77" t="s">
+        <v>121</v>
+      </c>
+      <c r="C77" t="s">
         <v>241</v>
       </c>
-      <c r="B77" t="s">
-        <v>122</v>
-      </c>
-      <c r="C77" t="s">
-        <v>242</v>
-      </c>
       <c r="D77" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E77" t="s">
+        <v>123</v>
+      </c>
+      <c r="F77" t="s">
         <v>124</v>
-      </c>
-      <c r="F77" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B78" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C78" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="D78" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E78" t="s">
+        <v>126</v>
+      </c>
+      <c r="F78" t="s">
         <v>127</v>
-      </c>
-      <c r="F78" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B79" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C79" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="D79" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E79" t="s">
+        <v>129</v>
+      </c>
+      <c r="F79" t="s">
         <v>130</v>
-      </c>
-      <c r="F79" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
+        <v>244</v>
+      </c>
+      <c r="B80" t="s">
+        <v>121</v>
+      </c>
+      <c r="C80" t="s">
         <v>245</v>
       </c>
-      <c r="B80" t="s">
-        <v>122</v>
-      </c>
-      <c r="C80" t="s">
-        <v>246</v>
-      </c>
       <c r="D80" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E80" t="s">
+        <v>123</v>
+      </c>
+      <c r="F80" t="s">
         <v>124</v>
-      </c>
-      <c r="F80" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B81" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C81" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D81" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E81" t="s">
+        <v>126</v>
+      </c>
+      <c r="F81" t="s">
         <v>127</v>
-      </c>
-      <c r="F81" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B82" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C82" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D82" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E82" t="s">
+        <v>129</v>
+      </c>
+      <c r="F82" t="s">
         <v>130</v>
-      </c>
-      <c r="F82" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
+        <v>248</v>
+      </c>
+      <c r="B83" t="s">
+        <v>121</v>
+      </c>
+      <c r="C83" t="s">
         <v>249</v>
       </c>
-      <c r="B83" t="s">
-        <v>122</v>
-      </c>
-      <c r="C83" t="s">
+      <c r="D83" t="s">
         <v>250</v>
       </c>
-      <c r="D83" t="s">
-        <v>251</v>
-      </c>
       <c r="E83" t="s">
+        <v>123</v>
+      </c>
+      <c r="F83" t="s">
         <v>124</v>
-      </c>
-      <c r="F83" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B84" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C84" t="s">
+        <v>249</v>
+      </c>
+      <c r="D84" t="s">
         <v>250</v>
       </c>
-      <c r="D84" t="s">
-        <v>251</v>
-      </c>
       <c r="E84" t="s">
+        <v>126</v>
+      </c>
+      <c r="F84" t="s">
         <v>127</v>
-      </c>
-      <c r="F84" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B85" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C85" t="s">
+        <v>249</v>
+      </c>
+      <c r="D85" t="s">
         <v>250</v>
       </c>
-      <c r="D85" t="s">
-        <v>251</v>
-      </c>
       <c r="E85" t="s">
+        <v>129</v>
+      </c>
+      <c r="F85" t="s">
         <v>130</v>
-      </c>
-      <c r="F85" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
+        <v>253</v>
+      </c>
+      <c r="B86" t="s">
+        <v>121</v>
+      </c>
+      <c r="C86" t="s">
         <v>254</v>
       </c>
-      <c r="B86" t="s">
-        <v>122</v>
-      </c>
-      <c r="C86" t="s">
+      <c r="D86" t="s">
         <v>255</v>
       </c>
-      <c r="D86" t="s">
-        <v>256</v>
-      </c>
       <c r="E86" t="s">
+        <v>123</v>
+      </c>
+      <c r="F86" t="s">
         <v>124</v>
-      </c>
-      <c r="F86" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B87" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C87" t="s">
+        <v>254</v>
+      </c>
+      <c r="D87" t="s">
         <v>255</v>
       </c>
-      <c r="D87" t="s">
-        <v>256</v>
-      </c>
       <c r="E87" t="s">
+        <v>126</v>
+      </c>
+      <c r="F87" t="s">
         <v>127</v>
-      </c>
-      <c r="F87" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B88" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C88" t="s">
+        <v>254</v>
+      </c>
+      <c r="D88" t="s">
         <v>255</v>
       </c>
-      <c r="D88" t="s">
-        <v>256</v>
-      </c>
       <c r="E88" t="s">
+        <v>129</v>
+      </c>
+      <c r="F88" t="s">
         <v>130</v>
-      </c>
-      <c r="F88" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
+        <v>258</v>
+      </c>
+      <c r="B89" t="s">
+        <v>121</v>
+      </c>
+      <c r="C89" t="s">
         <v>259</v>
       </c>
-      <c r="B89" t="s">
-        <v>122</v>
-      </c>
-      <c r="C89" t="s">
-        <v>260</v>
-      </c>
       <c r="D89" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E89" t="s">
+        <v>123</v>
+      </c>
+      <c r="F89" t="s">
         <v>124</v>
-      </c>
-      <c r="F89" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B90" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C90" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E90" t="s">
+        <v>126</v>
+      </c>
+      <c r="F90" t="s">
         <v>127</v>
-      </c>
-      <c r="F90" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B91" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C91" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E91" t="s">
+        <v>129</v>
+      </c>
+      <c r="F91" t="s">
         <v>130</v>
-      </c>
-      <c r="F91" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
+        <v>262</v>
+      </c>
+      <c r="B92" t="s">
+        <v>121</v>
+      </c>
+      <c r="C92" t="s">
         <v>263</v>
       </c>
-      <c r="B92" t="s">
-        <v>122</v>
-      </c>
-      <c r="C92" t="s">
+      <c r="D92" t="s">
         <v>264</v>
       </c>
-      <c r="D92" t="s">
-        <v>265</v>
-      </c>
       <c r="E92" t="s">
+        <v>123</v>
+      </c>
+      <c r="F92" t="s">
         <v>124</v>
-      </c>
-      <c r="F92" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B93" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C93" t="s">
+        <v>263</v>
+      </c>
+      <c r="D93" t="s">
         <v>264</v>
       </c>
-      <c r="D93" t="s">
-        <v>265</v>
-      </c>
       <c r="E93" t="s">
+        <v>126</v>
+      </c>
+      <c r="F93" t="s">
         <v>127</v>
-      </c>
-      <c r="F93" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B94" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C94" t="s">
+        <v>263</v>
+      </c>
+      <c r="D94" t="s">
         <v>264</v>
       </c>
-      <c r="D94" t="s">
-        <v>265</v>
-      </c>
       <c r="E94" t="s">
+        <v>129</v>
+      </c>
+      <c r="F94" t="s">
         <v>130</v>
-      </c>
-      <c r="F94" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
+        <v>267</v>
+      </c>
+      <c r="B95" t="s">
+        <v>121</v>
+      </c>
+      <c r="C95" t="s">
         <v>268</v>
       </c>
-      <c r="B95" t="s">
-        <v>122</v>
-      </c>
-      <c r="C95" t="s">
+      <c r="D95" t="s">
         <v>269</v>
       </c>
-      <c r="D95" t="s">
-        <v>270</v>
-      </c>
       <c r="E95" t="s">
+        <v>123</v>
+      </c>
+      <c r="F95" t="s">
         <v>124</v>
-      </c>
-      <c r="F95" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B96" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C96" t="s">
+        <v>268</v>
+      </c>
+      <c r="D96" t="s">
         <v>269</v>
       </c>
-      <c r="D96" t="s">
-        <v>270</v>
-      </c>
       <c r="E96" t="s">
+        <v>126</v>
+      </c>
+      <c r="F96" t="s">
         <v>127</v>
-      </c>
-      <c r="F96" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B97" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C97" t="s">
+        <v>268</v>
+      </c>
+      <c r="D97" t="s">
         <v>269</v>
       </c>
-      <c r="D97" t="s">
-        <v>270</v>
-      </c>
       <c r="E97" t="s">
+        <v>129</v>
+      </c>
+      <c r="F97" t="s">
         <v>130</v>
-      </c>
-      <c r="F97" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
+        <v>272</v>
+      </c>
+      <c r="B98" t="s">
+        <v>121</v>
+      </c>
+      <c r="C98" t="s">
         <v>273</v>
       </c>
-      <c r="B98" t="s">
-        <v>122</v>
-      </c>
-      <c r="C98" t="s">
-        <v>274</v>
-      </c>
       <c r="D98" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E98" t="s">
+        <v>123</v>
+      </c>
+      <c r="F98" t="s">
         <v>124</v>
-      </c>
-      <c r="F98" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B99" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C99" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D99" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E99" t="s">
+        <v>126</v>
+      </c>
+      <c r="F99" t="s">
         <v>127</v>
-      </c>
-      <c r="F99" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B100" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C100" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D100" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E100" t="s">
+        <v>129</v>
+      </c>
+      <c r="F100" t="s">
         <v>130</v>
-      </c>
-      <c r="F100" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
+        <v>276</v>
+      </c>
+      <c r="B101" t="s">
+        <v>121</v>
+      </c>
+      <c r="C101" t="s">
         <v>277</v>
       </c>
-      <c r="B101" t="s">
-        <v>122</v>
-      </c>
-      <c r="C101" t="s">
-        <v>278</v>
-      </c>
       <c r="D101" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E101" t="s">
+        <v>123</v>
+      </c>
+      <c r="F101" t="s">
         <v>124</v>
-      </c>
-      <c r="F101" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B102" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C102" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D102" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E102" t="s">
+        <v>126</v>
+      </c>
+      <c r="F102" t="s">
         <v>127</v>
-      </c>
-      <c r="F102" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B103" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C103" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D103" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E103" t="s">
+        <v>129</v>
+      </c>
+      <c r="F103" t="s">
         <v>130</v>
-      </c>
-      <c r="F103" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
+        <v>280</v>
+      </c>
+      <c r="B104" t="s">
+        <v>121</v>
+      </c>
+      <c r="C104" t="s">
         <v>281</v>
       </c>
-      <c r="B104" t="s">
-        <v>122</v>
-      </c>
-      <c r="C104" t="s">
-        <v>282</v>
-      </c>
       <c r="D104" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E104" t="s">
+        <v>123</v>
+      </c>
+      <c r="F104" t="s">
         <v>124</v>
-      </c>
-      <c r="F104" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B105" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C105" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="D105" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E105" t="s">
+        <v>126</v>
+      </c>
+      <c r="F105" t="s">
         <v>127</v>
-      </c>
-      <c r="F105" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B106" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C106" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="D106" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E106" t="s">
+        <v>129</v>
+      </c>
+      <c r="F106" t="s">
         <v>130</v>
-      </c>
-      <c r="F106" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
+        <v>284</v>
+      </c>
+      <c r="B107" t="s">
+        <v>121</v>
+      </c>
+      <c r="C107" t="s">
         <v>285</v>
       </c>
-      <c r="B107" t="s">
-        <v>122</v>
-      </c>
-      <c r="C107" t="s">
-        <v>286</v>
-      </c>
       <c r="D107" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E107" t="s">
+        <v>123</v>
+      </c>
+      <c r="F107" t="s">
         <v>124</v>
-      </c>
-      <c r="F107" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B108" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C108" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D108" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E108" t="s">
+        <v>126</v>
+      </c>
+      <c r="F108" t="s">
         <v>127</v>
-      </c>
-      <c r="F108" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B109" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C109" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D109" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E109" t="s">
+        <v>129</v>
+      </c>
+      <c r="F109" t="s">
         <v>130</v>
-      </c>
-      <c r="F109" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
+        <v>288</v>
+      </c>
+      <c r="B110" t="s">
+        <v>121</v>
+      </c>
+      <c r="C110" t="s">
         <v>289</v>
       </c>
-      <c r="B110" t="s">
-        <v>122</v>
-      </c>
-      <c r="C110" t="s">
-        <v>290</v>
-      </c>
       <c r="D110" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E110" t="s">
+        <v>123</v>
+      </c>
+      <c r="F110" t="s">
         <v>124</v>
-      </c>
-      <c r="F110" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B111" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C111" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D111" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E111" t="s">
+        <v>126</v>
+      </c>
+      <c r="F111" t="s">
         <v>127</v>
-      </c>
-      <c r="F111" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B112" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C112" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D112" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E112" t="s">
+        <v>129</v>
+      </c>
+      <c r="F112" t="s">
         <v>130</v>
-      </c>
-      <c r="F112" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
+        <v>292</v>
+      </c>
+      <c r="B113" t="s">
+        <v>121</v>
+      </c>
+      <c r="C113" t="s">
         <v>293</v>
       </c>
-      <c r="B113" t="s">
-        <v>122</v>
-      </c>
-      <c r="C113" t="s">
-        <v>294</v>
-      </c>
       <c r="D113" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E113" t="s">
+        <v>123</v>
+      </c>
+      <c r="F113" t="s">
         <v>124</v>
-      </c>
-      <c r="F113" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B114" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C114" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="D114" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E114" t="s">
+        <v>126</v>
+      </c>
+      <c r="F114" t="s">
         <v>127</v>
-      </c>
-      <c r="F114" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B115" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C115" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="D115" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E115" t="s">
+        <v>129</v>
+      </c>
+      <c r="F115" t="s">
         <v>130</v>
-      </c>
-      <c r="F115" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
+        <v>296</v>
+      </c>
+      <c r="B116" t="s">
+        <v>121</v>
+      </c>
+      <c r="C116" t="s">
         <v>297</v>
       </c>
-      <c r="B116" t="s">
-        <v>122</v>
-      </c>
-      <c r="C116" t="s">
+      <c r="D116" t="s">
         <v>298</v>
       </c>
-      <c r="D116" t="s">
-        <v>299</v>
-      </c>
       <c r="E116" t="s">
+        <v>123</v>
+      </c>
+      <c r="F116" t="s">
         <v>124</v>
-      </c>
-      <c r="F116" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B117" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C117" t="s">
+        <v>297</v>
+      </c>
+      <c r="D117" t="s">
         <v>298</v>
       </c>
-      <c r="D117" t="s">
-        <v>299</v>
-      </c>
       <c r="E117" t="s">
+        <v>126</v>
+      </c>
+      <c r="F117" t="s">
         <v>127</v>
-      </c>
-      <c r="F117" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B118" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C118" t="s">
+        <v>297</v>
+      </c>
+      <c r="D118" t="s">
         <v>298</v>
       </c>
-      <c r="D118" t="s">
-        <v>299</v>
-      </c>
       <c r="E118" t="s">
+        <v>129</v>
+      </c>
+      <c r="F118" t="s">
         <v>130</v>
-      </c>
-      <c r="F118" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
+        <v>301</v>
+      </c>
+      <c r="B119" t="s">
+        <v>121</v>
+      </c>
+      <c r="C119" t="s">
         <v>302</v>
       </c>
-      <c r="B119" t="s">
-        <v>122</v>
-      </c>
-      <c r="C119" t="s">
-        <v>303</v>
-      </c>
       <c r="D119" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E119" t="s">
+        <v>123</v>
+      </c>
+      <c r="F119" t="s">
         <v>124</v>
-      </c>
-      <c r="F119" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B120" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C120" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="D120" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E120" t="s">
+        <v>126</v>
+      </c>
+      <c r="F120" t="s">
         <v>127</v>
-      </c>
-      <c r="F120" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B121" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C121" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="D121" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E121" t="s">
+        <v>129</v>
+      </c>
+      <c r="F121" t="s">
         <v>130</v>
-      </c>
-      <c r="F121" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
+        <v>305</v>
+      </c>
+      <c r="B122" t="s">
+        <v>121</v>
+      </c>
+      <c r="C122" t="s">
         <v>306</v>
       </c>
-      <c r="B122" t="s">
-        <v>122</v>
-      </c>
-      <c r="C122" t="s">
-        <v>307</v>
-      </c>
       <c r="D122" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E122" t="s">
+        <v>123</v>
+      </c>
+      <c r="F122" t="s">
         <v>124</v>
-      </c>
-      <c r="F122" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B123" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C123" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="D123" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E123" t="s">
+        <v>126</v>
+      </c>
+      <c r="F123" t="s">
         <v>127</v>
-      </c>
-      <c r="F123" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B124" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C124" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="D124" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E124" t="s">
+        <v>129</v>
+      </c>
+      <c r="F124" t="s">
         <v>130</v>
-      </c>
-      <c r="F124" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
+        <v>309</v>
+      </c>
+      <c r="B125" t="s">
+        <v>121</v>
+      </c>
+      <c r="C125" t="s">
         <v>310</v>
       </c>
-      <c r="B125" t="s">
-        <v>122</v>
-      </c>
-      <c r="C125" t="s">
-        <v>311</v>
-      </c>
       <c r="D125" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E125" t="s">
+        <v>123</v>
+      </c>
+      <c r="F125" t="s">
         <v>124</v>
-      </c>
-      <c r="F125" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B126" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C126" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D126" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E126" t="s">
+        <v>126</v>
+      </c>
+      <c r="F126" t="s">
         <v>127</v>
-      </c>
-      <c r="F126" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B127" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C127" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D127" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E127" t="s">
+        <v>129</v>
+      </c>
+      <c r="F127" t="s">
         <v>130</v>
-      </c>
-      <c r="F127" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
+        <v>313</v>
+      </c>
+      <c r="B128" t="s">
+        <v>121</v>
+      </c>
+      <c r="C128" t="s">
         <v>314</v>
       </c>
-      <c r="B128" t="s">
-        <v>122</v>
-      </c>
-      <c r="C128" t="s">
+      <c r="D128" t="s">
         <v>315</v>
       </c>
-      <c r="D128" t="s">
-        <v>316</v>
-      </c>
       <c r="E128" t="s">
+        <v>123</v>
+      </c>
+      <c r="F128" t="s">
         <v>124</v>
-      </c>
-      <c r="F128" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B129" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C129" t="s">
+        <v>314</v>
+      </c>
+      <c r="D129" t="s">
         <v>315</v>
       </c>
-      <c r="D129" t="s">
-        <v>316</v>
-      </c>
       <c r="E129" t="s">
+        <v>126</v>
+      </c>
+      <c r="F129" t="s">
         <v>127</v>
-      </c>
-      <c r="F129" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B130" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C130" t="s">
+        <v>314</v>
+      </c>
+      <c r="D130" t="s">
         <v>315</v>
       </c>
-      <c r="D130" t="s">
-        <v>316</v>
-      </c>
       <c r="E130" t="s">
+        <v>129</v>
+      </c>
+      <c r="F130" t="s">
         <v>130</v>
-      </c>
-      <c r="F130" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
+        <v>318</v>
+      </c>
+      <c r="B131" t="s">
+        <v>121</v>
+      </c>
+      <c r="C131" t="s">
         <v>319</v>
       </c>
-      <c r="B131" t="s">
-        <v>122</v>
-      </c>
-      <c r="C131" t="s">
-        <v>320</v>
-      </c>
       <c r="D131" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E131" t="s">
+        <v>123</v>
+      </c>
+      <c r="F131" t="s">
         <v>124</v>
-      </c>
-      <c r="F131" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B132" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C132" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="D132" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E132" t="s">
+        <v>126</v>
+      </c>
+      <c r="F132" t="s">
         <v>127</v>
-      </c>
-      <c r="F132" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B133" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C133" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="D133" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E133" t="s">
+        <v>129</v>
+      </c>
+      <c r="F133" t="s">
         <v>130</v>
-      </c>
-      <c r="F133" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
+        <v>322</v>
+      </c>
+      <c r="B134" t="s">
+        <v>121</v>
+      </c>
+      <c r="C134" t="s">
         <v>323</v>
       </c>
-      <c r="B134" t="s">
-        <v>122</v>
-      </c>
-      <c r="C134" t="s">
-        <v>324</v>
-      </c>
       <c r="D134" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E134" t="s">
+        <v>123</v>
+      </c>
+      <c r="F134" t="s">
         <v>124</v>
-      </c>
-      <c r="F134" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B135" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C135" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="D135" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E135" t="s">
+        <v>126</v>
+      </c>
+      <c r="F135" t="s">
         <v>127</v>
-      </c>
-      <c r="F135" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B136" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C136" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="D136" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E136" t="s">
+        <v>129</v>
+      </c>
+      <c r="F136" t="s">
         <v>130</v>
-      </c>
-      <c r="F136" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
+        <v>326</v>
+      </c>
+      <c r="B137" t="s">
+        <v>121</v>
+      </c>
+      <c r="C137" t="s">
         <v>327</v>
       </c>
-      <c r="B137" t="s">
-        <v>122</v>
-      </c>
-      <c r="C137" t="s">
+      <c r="D137" t="s">
         <v>328</v>
       </c>
-      <c r="D137" t="s">
-        <v>329</v>
-      </c>
       <c r="E137" t="s">
+        <v>123</v>
+      </c>
+      <c r="F137" t="s">
         <v>124</v>
-      </c>
-      <c r="F137" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B138" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C138" t="s">
+        <v>327</v>
+      </c>
+      <c r="D138" t="s">
         <v>328</v>
       </c>
-      <c r="D138" t="s">
-        <v>329</v>
-      </c>
       <c r="E138" t="s">
+        <v>126</v>
+      </c>
+      <c r="F138" t="s">
         <v>127</v>
-      </c>
-      <c r="F138" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B139" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C139" t="s">
+        <v>327</v>
+      </c>
+      <c r="D139" t="s">
         <v>328</v>
       </c>
-      <c r="D139" t="s">
-        <v>329</v>
-      </c>
       <c r="E139" t="s">
+        <v>129</v>
+      </c>
+      <c r="F139" t="s">
         <v>130</v>
-      </c>
-      <c r="F139" t="s">
-        <v>131</v>
       </c>
     </row>
   </sheetData>
